--- a/docs/deliverables/out/Drop-2_Independent/BRD-08_Employee_Benefits/BIBS_TestPlan_BRD-08_Employee_Benefits_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-2_Independent/BRD-08_Employee_Benefits/BIBS_TestPlan_BRD-08_Employee_Benefits_v1.0.xlsx
@@ -16,11 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles and Access" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRS Findings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="10" state="hidden" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Document Control'!$A$4:$F$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Document Control'!$4:$4</definedName>
@@ -28,16 +27,14 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Test Conditions'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Scenarios'!$A$4:$F$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Scenarios'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Cases'!$A$4:$R$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Cases'!$A$4:$Q$158</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Test Cases'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Coverage'!$A$4:$J$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Coverage'!$A$4:$I$77</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Coverage'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Test Data'!$A$4:$E$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Test Data'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Roles and Access'!$A$4:$M$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Roles and Access'!$A$4:$L$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Roles and Access'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'FRS Findings'!$A$4:$D$13</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'FRS Findings'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +435,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="971550" cy="285750"/>
@@ -751,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E39"/>
+  <dimension ref="B4:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1010,92 +1007,77 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>FRS points raised for the FRS owner; the affected cases assume the proposed resolution</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>9</v>
+    <row r="29">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Legend</t>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>The case ran and the actual result matches the expected result</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>The case ran and the actual result matches the expected result</t>
+          <t>The actual result differs; an issue ID is recorded</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>The actual result differs; a defect ID is recorded</t>
+          <t>The case cannot run (environment, data or an open issue elsewhere)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>The case cannot run (environment, data or a defect elsewhere)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
           <t>Not applicable in this cycle, with the reason in Actual result</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Source: FRS BRD-8 Employee Benefits. 39 FRs, 34 BRD IDs, 109 test conditions, 7 scenarios, 154 test cases (75 positive, 79 negative).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>Source: FRS BRD-8 (FRS_BRD08_EMPLOYEE_BENEFITS.md). 39 FRs, 34 BRD IDs, 109 test conditions, 7 scenarios, 154 test cases (75 positive, 79 negative), 0 with an automation reference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>Status starts as Not run. Testers fill Status, Actual result, Tester, Date and Defect ID during execution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="B39" s="20" t="inlineStr">
+          <t>Status starts as Not run. Testers fill Status, Actual result, Tester, Date and Issue ID during execution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>Prepared by iorta TechNXT for BDOI. Confidential – BDOI.</t>
         </is>
@@ -1111,7 +1093,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId9"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -1124,7 +1105,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -1132,288 +1113,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>FRS points raised for the FRS owner; the affected cases assume the proposed resolution</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="6" customHeight="1">
-      <c r="A3" s="25" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="26" t="inlineStr">
-        <is>
-          <t>FR ID</t>
-        </is>
-      </c>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>Finding</t>
-        </is>
-      </c>
-      <c r="D4" s="26" t="inlineStr">
-        <is>
-          <t>Proposed resolution</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>TF-EB-01</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>FR-EB-012</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>The FRS texts of the platform attachment codes differ from what BIBS shows - ATTACHMENT_TYPE_NOT_ALLOWED "The file type is not allowed" (built "Only these file types are allowed - &lt;list&gt;"), ATTACHMENT_TOO_LARGE "The file is larger than the allowed size" (built "The file exceeds the maximum size of &lt;n&gt; MB"), ATTACHMENT_INFECTED "The file failed the virus check" (built "The file was rejected by the malware scan - &lt;detail&gt;"). The same applies to FR-EB-002, 023, 030 and 031.</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Quote the platform texts in FRS v1.1; the cases use them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>TF-EB-02</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>FR-EB-020</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>The FRS gives CLIENT_DUPLICATE "A client with the same identifiers already exists" and CLIENT_NAME_REQUIRED "Enter the client name"; the client service shows "This client already exists - &lt;client&gt;" and "Enter the &lt;field&gt;".</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Quote the built texts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>TF-EB-03</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>FR-EB-004</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>EMAIL_ADDRESS_INVALID is given as "Enter a valid e-mail address"; the platform returns "Invalid e-mail address - &lt;address&gt;".</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Quote the platform text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>TF-EB-04</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>FR-EB-060</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>FR-EB-060 and 061 pair INVALID_REPORT_PARAMETERS with "The end date must be on or after the start date"; the report engine builds "&lt;to&gt; must not be before &lt;from&gt;" from the parameter labels.</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Quote the engine pattern.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>TF-EB-05</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>FR-EB-010</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Acceptance criterion 3 of FR-EB-010 says "The fourth failed sign-in locks the portal user" while rule R3 says lockout after 3 failed sign-ins (PORTAL_MAX_FAILED_LOGINS = 3). The cases lock at the third failure.</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Align the acceptance criterion with R3 ("the third failed sign-in locks the portal user, and the fourth is refused").</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>TF-EB-06</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>FR-EB-022</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>The RA lead time is 135 days (TAT annex) against the BRD example of 180 days (EBQ02), and who sets the renewal flag is open (EBQ03); the RA timing cases depend on both.</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Answer EBQ02 and EBQ03 before UAT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>TF-EB-07</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>FR-EB-031</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>The BOR is required for new business and remarketing renewals, while the BRD negative scenario says a BOR uploaded for a renewal is invalid (EBQ05). A renewal that stays with the incumbent has no BOR case.</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Answer EBQ05; add a case for a renewal without remarketing once decided.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>TF-EB-08</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>FR-EB-042</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>The threshold values, measure and approver levels are seed values (EBQ11); the FRS does not say whether "meets" means at or above the amount.</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>State "at or above" and give the BDOI values; the cases use the seed values.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>TF-EB-09</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>FR-EB-062</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>The TAT annex gives ranges ("1-5 working days"); the FRS parameters hold one value, and the start and stop events are open (EBQ21), so a breach cannot be tested except against the upper value.</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Confirm that the upper value of each range is the target and name the start and stop events.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:D13"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A5:D513">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Plan BRD-8 Employee Benefits&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
-    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,6 +1264,20 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>Upload-download</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Message</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2057,7 +1773,7 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Positive, Negative, Boundary, Security-access, Workflow, Report-output, Upload-download</t>
+          <t>Positive, Negative, Boundary, Security-access, Workflow, Report-output, Upload-download, Screen, Message</t>
         </is>
       </c>
     </row>
@@ -2074,7 +1790,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
+          <t>Role code and name (and the SIT/UAT user)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2146,7 +1862,7 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>What the system must do, with the exact message text and, for built BRDs, its code</t>
+          <t>What the system must do, with the exact message text and, where the system shows one, its code</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr"/>
@@ -2181,15 +1897,19 @@
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Existing automated test (class#method) that covers the case; blank when none</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr"/>
+          <t>Execution status</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Not run, Pass, Fail, Blocked, N/A</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -2199,19 +1919,15 @@
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Execution status</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="inlineStr">
-        <is>
-          <t>Not run, Pass, Fail, Blocked, N/A</t>
-        </is>
-      </c>
+          <t>What happened, filled by the tester</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -2221,12 +1937,12 @@
       </c>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>What happened, filled by the tester</t>
+          <t>Who ran the case</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr"/>
@@ -2239,12 +1955,12 @@
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Who ran the case</t>
+          <t>Date of the run</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr"/>
@@ -2257,12 +1973,12 @@
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Issue ID</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Date of the run</t>
+          <t>Issue raised when the case fails</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr"/>
@@ -2270,17 +1986,17 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Test Cases</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>Defect ID</t>
+          <t>FR / BRD ID</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Defect raised when the case fails</t>
+          <t>FR of the FRS, then BRD requirement ID</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr"/>
@@ -2293,12 +2009,12 @@
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>FR / BRD ID</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>FR of the FRS, then BRD requirement ID</t>
+          <t>FR or BRD ID</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr"/>
@@ -2311,12 +2027,12 @@
       </c>
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>FR or BRD ID</t>
+          <t>FR title</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr"/>
@@ -2329,12 +2045,12 @@
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Traces</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>FR title</t>
+          <t>BRD IDs of the FR, or FRs of the BRD ID</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr"/>
@@ -2347,12 +2063,12 @@
       </c>
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>Traces</t>
+          <t>Conditions</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>BRD IDs of the FR, or FRs of the BRD ID</t>
+          <t>Test conditions</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr"/>
@@ -2365,12 +2081,12 @@
       </c>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>Conditions</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Test conditions</t>
+          <t>Cases where the action succeeds</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr"/>
@@ -2383,12 +2099,12 @@
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Cases where the action succeeds</t>
+          <t>Cases where BIBS refuses the action</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr"/>
@@ -2401,12 +2117,12 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Cases where BIBS refuses the action</t>
+          <t>All cases</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr"/>
@@ -2419,30 +2135,34 @@
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>All cases</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="inlineStr"/>
+          <t>Covered: at least one positive and one negative case (FR) or one case (BRD ID); GAP otherwise</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>Covered, GAP</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Test Data</t>
         </is>
       </c>
       <c r="B49" s="22" t="inlineStr">
         <is>
-          <t>Automated</t>
+          <t>Data set</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Cases with an automation reference</t>
+          <t>Data set ID</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr"/>
@@ -2450,24 +2170,20 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Test Data</t>
         </is>
       </c>
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Covered: at least one positive and one negative case (FR) or one case (BRD ID); GAP otherwise</t>
-        </is>
-      </c>
-      <c r="D50" s="14" t="inlineStr">
-        <is>
-          <t>Covered, GAP</t>
-        </is>
-      </c>
+          <t>Short name used in the cases</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -2477,12 +2193,12 @@
       </c>
       <c r="B51" s="22" t="inlineStr">
         <is>
-          <t>Data set</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Data set ID</t>
+          <t>Records and values in the set</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr"/>
@@ -2495,12 +2211,12 @@
       </c>
       <c r="B52" s="23" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Short name used in the cases</t>
+          <t>Seed data set that provides it, or how the tester prepares it; non-production data is masked</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr"/>
@@ -2513,12 +2229,12 @@
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Cases</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Records and values in the set</t>
+          <t>Number of cases that use it</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr"/>
@@ -2526,17 +2242,17 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Test Data</t>
+          <t>Roles and Access</t>
         </is>
       </c>
       <c r="B54" s="23" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Case ID</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Access case ID: AC-&lt;code&gt;-&lt;nn&gt;.&lt;n&gt;</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -2544,17 +2260,17 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Test Data</t>
+          <t>Roles and Access</t>
         </is>
       </c>
       <c r="B55" s="22" t="inlineStr">
         <is>
-          <t>Cases</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Number of cases that use it</t>
+          <t>Screen or action checked</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr"/>
@@ -2567,12 +2283,12 @@
       </c>
       <c r="B56" s="23" t="inlineStr">
         <is>
-          <t>Case ID</t>
+          <t>Screen (menu path)</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Access case ID: AC-&lt;code&gt;-&lt;nn&gt;.&lt;n&gt;</t>
+          <t>Where it is done</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr"/>
@@ -2585,12 +2301,12 @@
       </c>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Permission</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Screen or action checked</t>
+          <t>BIBS permission that grants it</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr"/>
@@ -2603,12 +2319,12 @@
       </c>
       <c r="B58" s="23" t="inlineStr">
         <is>
-          <t>Screen (menu path)</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Where it is done</t>
+          <t>Role tested (log in as a user who holds only this role)</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr"/>
@@ -2621,15 +2337,19 @@
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>BIBS permission that grants it</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="inlineStr"/>
+          <t>Expected access</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>Allowed, Denied</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
@@ -2639,12 +2359,12 @@
       </c>
       <c r="B60" s="23" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Expected result</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Role tested (log in as a user who holds only this role)</t>
+          <t>What the user sees</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr"/>
@@ -2657,17 +2377,17 @@
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>Access</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Expected access</t>
+          <t>Execution status</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Allowed, Denied</t>
+          <t>Not run, Pass, Fail, Blocked, N/A</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2399,12 @@
       </c>
       <c r="B62" s="23" t="inlineStr">
         <is>
-          <t>Expected result</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>What the user sees</t>
+          <t>Filled by the tester</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr"/>
@@ -2697,12 +2417,12 @@
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Existing automated test, if any</t>
+          <t>Who ran the case</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr"/>
@@ -2715,19 +2435,15 @@
       </c>
       <c r="B64" s="23" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Execution status</t>
-        </is>
-      </c>
-      <c r="D64" s="14" t="inlineStr">
-        <is>
-          <t>Not run, Pass, Fail, Blocked, N/A</t>
-        </is>
-      </c>
+          <t>Date of the run</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -2737,144 +2453,18 @@
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Issue ID</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Filled by the tester</t>
+          <t>Issue raised when the case fails</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr"/>
     </row>
-    <row r="66">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B66" s="23" t="inlineStr">
-        <is>
-          <t>Tester</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="inlineStr">
-        <is>
-          <t>Who ran the case</t>
-        </is>
-      </c>
-      <c r="D66" s="14" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B67" s="22" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="inlineStr">
-        <is>
-          <t>Date of the run</t>
-        </is>
-      </c>
-      <c r="D67" s="12" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="14" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B68" s="23" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="inlineStr">
-        <is>
-          <t>Defect raised when the case fails</t>
-        </is>
-      </c>
-      <c r="D68" s="14" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="12" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B69" s="22" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C69" s="12" t="inlineStr">
-        <is>
-          <t>Finding ID</t>
-        </is>
-      </c>
-      <c r="D69" s="12" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="14" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B70" s="23" t="inlineStr">
-        <is>
-          <t>FR ID</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="inlineStr">
-        <is>
-          <t>FR concerned</t>
-        </is>
-      </c>
-      <c r="D70" s="14" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="12" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B71" s="22" t="inlineStr">
-        <is>
-          <t>Finding</t>
-        </is>
-      </c>
-      <c r="C71" s="12" t="inlineStr">
-        <is>
-          <t>Ambiguous or untestable point found while writing the cases</t>
-        </is>
-      </c>
-      <c r="D71" s="12" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="14" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B72" s="23" t="inlineStr">
-        <is>
-          <t>Proposed resolution</t>
-        </is>
-      </c>
-      <c r="C72" s="14" t="inlineStr">
-        <is>
-          <t>What the test team proposes to the FRS owner</t>
-        </is>
-      </c>
-      <c r="D72" s="14" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:D72"/>
+  <autoFilter ref="A4:D65"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -2984,7 +2574,7 @@
       <c r="E5" s="12" t="inlineStr"/>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Internal draft from FRS BRD-8 v1.0 and the Employee Benefits build design</t>
+          <t>Internal draft from FRS BRD-8 v1.0</t>
         </is>
       </c>
     </row>
@@ -3165,7 +2755,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>A direct call without the permission is refused (HTTP 403) and logged.</t>
+          <t>A direct request without the permission is refused and logged.</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -3197,7 +2787,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Insurer and client HR users never reach the core BIBS screens or API.</t>
+          <t>Insurer and client HR users never reach the core BIBS screens or services.</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -3517,7 +3107,7 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>The core API refuses portal tokens; a record of another party answers not found and is logged.</t>
+          <t>The core BIBS services refuse portal sign-ins; a record of another party answers not found and is logged.</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -5149,7 +4739,7 @@
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>The comparative is built from the validated proposals with one column per insurer, coverage per TOR item, premiums, exclusions and capability factors, and stored as a snapshot version.</t>
+          <t>The comparative is prepared from the validated proposals with one column per insurer, coverage per TOR item, premiums, exclusions and capability factors, and stored as a snapshot version.</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
@@ -5309,7 +4899,7 @@
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Rules are maintained with maker-checker and apply after authorisation without a new build; an amount must be greater than zero.</t>
+          <t>Rules are maintained with maker-checker and apply after authorisation, without a change to the system; an amount must be greater than zero.</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
@@ -6841,7 +6431,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Proposals to placement. Insurers submit proposals; the AO validates them, builds the comparative; the signatory and Management approve; the client comments, asks for revisions and confirms; the AO triggers placement.</t>
+          <t>Proposals to placement. Insurers submit proposals; the AO validates them and prepares the comparative; the signatory and Management approve; the client comments, asks for revisions and confirms; the AO triggers placement.</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -6943,7 +6533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R158"/>
+  <dimension ref="A1:Q158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6958,12 +6548,11 @@
     <col width="52" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -6998,7 +6587,6 @@
       <c r="O3" s="25" t="n"/>
       <c r="P3" s="25" t="n"/>
       <c r="Q3" s="25" t="n"/>
-      <c r="R3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -7063,32 +6651,27 @@
       </c>
       <c r="M4" s="26" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="N4" s="26" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="O4" s="26" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="P4" s="26" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="26" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="26" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
+          <t>Issue ID</t>
         </is>
       </c>
     </row>
@@ -7153,16 +6736,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M5" s="12" t="inlineStr"/>
-      <c r="N5" s="27" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N5" s="12" t="n"/>
       <c r="O5" s="12" t="n"/>
-      <c r="P5" s="12" t="n"/>
-      <c r="Q5" s="28" t="n"/>
-      <c r="R5" s="12" t="n"/>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -7225,16 +6807,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="27" t="inlineStr">
+      <c r="M6" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N6" s="12" t="n"/>
       <c r="O6" s="12" t="n"/>
-      <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="28" t="n"/>
-      <c r="R6" s="12" t="n"/>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -7284,12 +6865,12 @@
       </c>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>1. As a Renewal AO (no EB role) open Reports; call the EB-PRODUCTION run endpoint.</t>
+          <t>1. As a Renewal AO (no EB role) open Reports; send a direct request to run EB-PRODUCTION.</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>The Employee Benefits category is not listed; the call returns HTTP 403 and is logged with user, endpoint and time.
+          <t>The Employee Benefits category is not listed; the request is refused and is logged with the user and time.
 Message "You are not permitted to perform this action".</t>
         </is>
       </c>
@@ -7298,16 +6879,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="27" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N7" s="12" t="n"/>
       <c r="O7" s="12" t="n"/>
-      <c r="P7" s="12" t="n"/>
-      <c r="Q7" s="28" t="n"/>
-      <c r="R7" s="12" t="n"/>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -7332,7 +6912,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Portal token refused by the core API</t>
+          <t>Portal sign-in refused by the core BIBS services</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -7347,7 +6927,7 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr">
@@ -7357,12 +6937,12 @@
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>1. With ins.a's portal token call GET /api/v1/accounts.</t>
+          <t>1. Signed in as ins.a on the portal, send a direct request to list the BIBS accounts.</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>The call is refused; no data is returned.</t>
+          <t>The request is refused; no data is returned.</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
@@ -7370,16 +6950,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="27" t="inlineStr">
+      <c r="M8" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N8" s="12" t="n"/>
       <c r="O8" s="12" t="n"/>
-      <c r="P8" s="12" t="n"/>
-      <c r="Q8" s="28" t="n"/>
-      <c r="R8" s="12" t="n"/>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -7443,16 +7022,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="27" t="inlineStr">
+      <c r="M9" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N9" s="12" t="n"/>
       <c r="O9" s="12" t="n"/>
-      <c r="P9" s="12" t="n"/>
-      <c r="Q9" s="28" t="n"/>
-      <c r="R9" s="12" t="n"/>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -7507,7 +7085,7 @@
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>The utilization report (Marketing only) is not listed; a direct download call is refused and logged.</t>
+          <t>The utilization report (Marketing only) is not listed; a direct download request is refused and logged.</t>
         </is>
       </c>
       <c r="L10" s="12" t="inlineStr">
@@ -7515,16 +7093,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="27" t="inlineStr">
+      <c r="M10" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N10" s="12" t="n"/>
       <c r="O10" s="12" t="n"/>
-      <c r="P10" s="12" t="n"/>
-      <c r="Q10" s="28" t="n"/>
-      <c r="R10" s="12" t="n"/>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -7588,16 +7165,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="27" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N11" s="12" t="n"/>
       <c r="O11" s="12" t="n"/>
-      <c r="P11" s="12" t="n"/>
-      <c r="Q11" s="28" t="n"/>
-      <c r="R11" s="12" t="n"/>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -7661,16 +7237,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="27" t="inlineStr">
+      <c r="M12" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N12" s="12" t="n"/>
       <c r="O12" s="12" t="n"/>
-      <c r="P12" s="12" t="n"/>
-      <c r="Q12" s="28" t="n"/>
-      <c r="R12" s="12" t="n"/>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -7733,16 +7308,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="27" t="inlineStr">
+      <c r="M13" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N13" s="12" t="n"/>
       <c r="O13" s="12" t="n"/>
-      <c r="P13" s="12" t="n"/>
-      <c r="Q13" s="28" t="n"/>
-      <c r="R13" s="12" t="n"/>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -7805,16 +7379,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="27" t="inlineStr">
+      <c r="M14" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N14" s="12" t="n"/>
       <c r="O14" s="12" t="n"/>
-      <c r="P14" s="12" t="n"/>
-      <c r="Q14" s="28" t="n"/>
-      <c r="R14" s="12" t="n"/>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -7854,7 +7427,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
@@ -7864,12 +7437,12 @@
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>1. Look for edit on the History tab and on version 1; call PUT on version 1.</t>
+          <t>1. Look for edit on the History tab and on version 1; send a direct request to change version 1.</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>No edit exists; the call is refused.</t>
+          <t>No edit exists; a direct request is refused.</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
@@ -7877,16 +7450,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="27" t="inlineStr">
+      <c r="M15" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N15" s="12" t="n"/>
       <c r="O15" s="12" t="n"/>
-      <c r="P15" s="12" t="n"/>
-      <c r="Q15" s="28" t="n"/>
-      <c r="R15" s="12" t="n"/>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -7949,16 +7521,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M16" s="12" t="inlineStr"/>
-      <c r="N16" s="27" t="inlineStr">
+      <c r="M16" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N16" s="12" t="n"/>
       <c r="O16" s="12" t="n"/>
-      <c r="P16" s="12" t="n"/>
-      <c r="Q16" s="28" t="n"/>
-      <c r="R16" s="12" t="n"/>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -8022,16 +7593,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="27" t="inlineStr">
+      <c r="M17" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N17" s="12" t="n"/>
       <c r="O17" s="12" t="n"/>
-      <c r="P17" s="12" t="n"/>
-      <c r="Q17" s="28" t="n"/>
-      <c r="R17" s="12" t="n"/>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -8095,16 +7665,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M18" s="12" t="inlineStr"/>
-      <c r="N18" s="27" t="inlineStr">
+      <c r="M18" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N18" s="12" t="n"/>
       <c r="O18" s="12" t="n"/>
-      <c r="P18" s="12" t="n"/>
-      <c r="Q18" s="28" t="n"/>
-      <c r="R18" s="12" t="n"/>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -8167,16 +7736,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="27" t="inlineStr">
+      <c r="M19" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N19" s="12" t="n"/>
       <c r="O19" s="12" t="n"/>
-      <c r="P19" s="12" t="n"/>
-      <c r="Q19" s="28" t="n"/>
-      <c r="R19" s="12" t="n"/>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -8216,7 +7784,7 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
@@ -8226,7 +7794,7 @@
       </c>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>1. As ins.b call the portal endpoint of an INS-A request.</t>
+          <t>1. As ins.b send a direct portal request of an INS-A request.</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
@@ -8239,16 +7807,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M20" s="12" t="inlineStr"/>
-      <c r="N20" s="27" t="inlineStr">
+      <c r="M20" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N20" s="12" t="n"/>
       <c r="O20" s="12" t="n"/>
-      <c r="P20" s="12" t="n"/>
-      <c r="Q20" s="28" t="n"/>
-      <c r="R20" s="12" t="n"/>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -8312,16 +7879,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M21" s="12" t="inlineStr"/>
-      <c r="N21" s="27" t="inlineStr">
+      <c r="M21" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N21" s="12" t="n"/>
       <c r="O21" s="12" t="n"/>
-      <c r="P21" s="12" t="n"/>
-      <c r="Q21" s="28" t="n"/>
-      <c r="R21" s="12" t="n"/>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -8385,16 +7951,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M22" s="12" t="inlineStr"/>
-      <c r="N22" s="27" t="inlineStr">
+      <c r="M22" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N22" s="12" t="n"/>
       <c r="O22" s="12" t="n"/>
-      <c r="P22" s="12" t="n"/>
-      <c r="Q22" s="28" t="n"/>
-      <c r="R22" s="12" t="n"/>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -8457,16 +8022,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M23" s="12" t="inlineStr"/>
-      <c r="N23" s="27" t="inlineStr">
+      <c r="M23" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N23" s="12" t="n"/>
       <c r="O23" s="12" t="n"/>
-      <c r="P23" s="12" t="n"/>
-      <c r="Q23" s="28" t="n"/>
-      <c r="R23" s="12" t="n"/>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -8530,16 +8094,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M24" s="12" t="inlineStr"/>
-      <c r="N24" s="27" t="inlineStr">
+      <c r="M24" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N24" s="12" t="n"/>
       <c r="O24" s="12" t="n"/>
-      <c r="P24" s="12" t="n"/>
-      <c r="Q24" s="28" t="n"/>
-      <c r="R24" s="12" t="n"/>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -8603,16 +8166,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M25" s="12" t="inlineStr"/>
-      <c r="N25" s="27" t="inlineStr">
+      <c r="M25" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N25" s="12" t="n"/>
       <c r="O25" s="12" t="n"/>
-      <c r="P25" s="12" t="n"/>
-      <c r="Q25" s="28" t="n"/>
-      <c r="R25" s="12" t="n"/>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -8675,16 +8237,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M26" s="12" t="inlineStr"/>
-      <c r="N26" s="27" t="inlineStr">
+      <c r="M26" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N26" s="12" t="n"/>
       <c r="O26" s="12" t="n"/>
-      <c r="P26" s="12" t="n"/>
-      <c r="Q26" s="28" t="n"/>
-      <c r="R26" s="12" t="n"/>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -8747,16 +8308,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M27" s="12" t="inlineStr"/>
-      <c r="N27" s="27" t="inlineStr">
+      <c r="M27" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N27" s="12" t="n"/>
       <c r="O27" s="12" t="n"/>
-      <c r="P27" s="12" t="n"/>
-      <c r="Q27" s="28" t="n"/>
-      <c r="R27" s="12" t="n"/>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -8820,16 +8380,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M28" s="12" t="inlineStr"/>
-      <c r="N28" s="27" t="inlineStr">
+      <c r="M28" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N28" s="12" t="n"/>
       <c r="O28" s="12" t="n"/>
-      <c r="P28" s="12" t="n"/>
-      <c r="Q28" s="28" t="n"/>
-      <c r="R28" s="12" t="n"/>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -8892,16 +8451,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M29" s="12" t="inlineStr"/>
-      <c r="N29" s="27" t="inlineStr">
+      <c r="M29" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N29" s="12" t="n"/>
       <c r="O29" s="12" t="n"/>
-      <c r="P29" s="12" t="n"/>
-      <c r="Q29" s="28" t="n"/>
-      <c r="R29" s="12" t="n"/>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -8964,16 +8522,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M30" s="12" t="inlineStr"/>
-      <c r="N30" s="27" t="inlineStr">
+      <c r="M30" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N30" s="12" t="n"/>
       <c r="O30" s="12" t="n"/>
-      <c r="P30" s="12" t="n"/>
-      <c r="Q30" s="28" t="n"/>
-      <c r="R30" s="12" t="n"/>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -9036,16 +8593,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M31" s="12" t="inlineStr"/>
-      <c r="N31" s="27" t="inlineStr">
+      <c r="M31" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N31" s="12" t="n"/>
       <c r="O31" s="12" t="n"/>
-      <c r="P31" s="12" t="n"/>
-      <c r="Q31" s="28" t="n"/>
-      <c r="R31" s="12" t="n"/>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -9109,16 +8665,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M32" s="12" t="inlineStr"/>
-      <c r="N32" s="27" t="inlineStr">
+      <c r="M32" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N32" s="12" t="n"/>
       <c r="O32" s="12" t="n"/>
-      <c r="P32" s="12" t="n"/>
-      <c r="Q32" s="28" t="n"/>
-      <c r="R32" s="12" t="n"/>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -9182,16 +8737,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M33" s="12" t="inlineStr"/>
-      <c r="N33" s="27" t="inlineStr">
+      <c r="M33" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N33" s="12" t="n"/>
       <c r="O33" s="12" t="n"/>
-      <c r="P33" s="12" t="n"/>
-      <c r="Q33" s="28" t="n"/>
-      <c r="R33" s="12" t="n"/>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -9254,16 +8808,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M34" s="12" t="inlineStr"/>
-      <c r="N34" s="27" t="inlineStr">
+      <c r="M34" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N34" s="12" t="n"/>
       <c r="O34" s="12" t="n"/>
-      <c r="P34" s="12" t="n"/>
-      <c r="Q34" s="28" t="n"/>
-      <c r="R34" s="12" t="n"/>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -9326,16 +8879,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M35" s="12" t="inlineStr"/>
-      <c r="N35" s="27" t="inlineStr">
+      <c r="M35" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N35" s="12" t="n"/>
       <c r="O35" s="12" t="n"/>
-      <c r="P35" s="12" t="n"/>
-      <c r="Q35" s="28" t="n"/>
-      <c r="R35" s="12" t="n"/>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -9385,7 +8937,7 @@
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>1. Open the INS-B proposal upload; Validate; open the comparative build list.</t>
+          <t>1. Open the INS-B proposal upload; Validate; open the list of proposals available for the comparative.</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
@@ -9398,16 +8950,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M36" s="12" t="inlineStr"/>
-      <c r="N36" s="27" t="inlineStr">
+      <c r="M36" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N36" s="12" t="n"/>
       <c r="O36" s="12" t="n"/>
-      <c r="P36" s="12" t="n"/>
-      <c r="Q36" s="28" t="n"/>
-      <c r="R36" s="12" t="n"/>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -9471,16 +9022,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M37" s="12" t="inlineStr"/>
-      <c r="N37" s="27" t="inlineStr">
+      <c r="M37" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N37" s="12" t="n"/>
       <c r="O37" s="12" t="n"/>
-      <c r="P37" s="12" t="n"/>
-      <c r="Q37" s="28" t="n"/>
-      <c r="R37" s="12" t="n"/>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -9543,16 +9093,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M38" s="12" t="inlineStr"/>
-      <c r="N38" s="27" t="inlineStr">
+      <c r="M38" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N38" s="12" t="n"/>
       <c r="O38" s="12" t="n"/>
-      <c r="P38" s="12" t="n"/>
-      <c r="Q38" s="28" t="n"/>
-      <c r="R38" s="12" t="n"/>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -9616,16 +9165,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M39" s="12" t="inlineStr"/>
-      <c r="N39" s="27" t="inlineStr">
+      <c r="M39" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N39" s="12" t="n"/>
       <c r="O39" s="12" t="n"/>
-      <c r="P39" s="12" t="n"/>
-      <c r="Q39" s="28" t="n"/>
-      <c r="R39" s="12" t="n"/>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -9688,16 +9236,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M40" s="12" t="inlineStr"/>
-      <c r="N40" s="27" t="inlineStr">
+      <c r="M40" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N40" s="12" t="n"/>
       <c r="O40" s="12" t="n"/>
-      <c r="P40" s="12" t="n"/>
-      <c r="Q40" s="28" t="n"/>
-      <c r="R40" s="12" t="n"/>
+      <c r="P40" s="28" t="n"/>
+      <c r="Q40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -9760,16 +9307,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M41" s="12" t="inlineStr"/>
-      <c r="N41" s="27" t="inlineStr">
+      <c r="M41" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N41" s="12" t="n"/>
       <c r="O41" s="12" t="n"/>
-      <c r="P41" s="12" t="n"/>
-      <c r="Q41" s="28" t="n"/>
-      <c r="R41" s="12" t="n"/>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -9833,16 +9379,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M42" s="12" t="inlineStr"/>
-      <c r="N42" s="27" t="inlineStr">
+      <c r="M42" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N42" s="12" t="n"/>
       <c r="O42" s="12" t="n"/>
-      <c r="P42" s="12" t="n"/>
-      <c r="Q42" s="28" t="n"/>
-      <c r="R42" s="12" t="n"/>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -9906,16 +9451,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M43" s="12" t="inlineStr"/>
-      <c r="N43" s="27" t="inlineStr">
+      <c r="M43" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N43" s="12" t="n"/>
       <c r="O43" s="12" t="n"/>
-      <c r="P43" s="12" t="n"/>
-      <c r="Q43" s="28" t="n"/>
-      <c r="R43" s="12" t="n"/>
+      <c r="P43" s="28" t="n"/>
+      <c r="Q43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -9978,16 +9522,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M44" s="12" t="inlineStr"/>
-      <c r="N44" s="27" t="inlineStr">
+      <c r="M44" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N44" s="12" t="n"/>
       <c r="O44" s="12" t="n"/>
-      <c r="P44" s="12" t="n"/>
-      <c r="Q44" s="28" t="n"/>
-      <c r="R44" s="12" t="n"/>
+      <c r="P44" s="28" t="n"/>
+      <c r="Q44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -10051,16 +9594,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M45" s="12" t="inlineStr"/>
-      <c r="N45" s="27" t="inlineStr">
+      <c r="M45" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N45" s="12" t="n"/>
       <c r="O45" s="12" t="n"/>
-      <c r="P45" s="12" t="n"/>
-      <c r="Q45" s="28" t="n"/>
-      <c r="R45" s="12" t="n"/>
+      <c r="P45" s="28" t="n"/>
+      <c r="Q45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -10124,16 +9666,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M46" s="12" t="inlineStr"/>
-      <c r="N46" s="27" t="inlineStr">
+      <c r="M46" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N46" s="12" t="n"/>
       <c r="O46" s="12" t="n"/>
-      <c r="P46" s="12" t="n"/>
-      <c r="Q46" s="28" t="n"/>
-      <c r="R46" s="12" t="n"/>
+      <c r="P46" s="28" t="n"/>
+      <c r="Q46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -10196,16 +9737,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M47" s="12" t="inlineStr"/>
-      <c r="N47" s="27" t="inlineStr">
+      <c r="M47" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N47" s="12" t="n"/>
       <c r="O47" s="12" t="n"/>
-      <c r="P47" s="12" t="n"/>
-      <c r="Q47" s="28" t="n"/>
-      <c r="R47" s="12" t="n"/>
+      <c r="P47" s="28" t="n"/>
+      <c r="Q47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -10268,16 +9808,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M48" s="12" t="inlineStr"/>
-      <c r="N48" s="27" t="inlineStr">
+      <c r="M48" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N48" s="12" t="n"/>
       <c r="O48" s="12" t="n"/>
-      <c r="P48" s="12" t="n"/>
-      <c r="Q48" s="28" t="n"/>
-      <c r="R48" s="12" t="n"/>
+      <c r="P48" s="28" t="n"/>
+      <c r="Q48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -10341,16 +9880,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M49" s="12" t="inlineStr"/>
-      <c r="N49" s="27" t="inlineStr">
+      <c r="M49" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N49" s="12" t="n"/>
       <c r="O49" s="12" t="n"/>
-      <c r="P49" s="12" t="n"/>
-      <c r="Q49" s="28" t="n"/>
-      <c r="R49" s="12" t="n"/>
+      <c r="P49" s="28" t="n"/>
+      <c r="Q49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -10414,16 +9952,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M50" s="12" t="inlineStr"/>
-      <c r="N50" s="27" t="inlineStr">
+      <c r="M50" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N50" s="12" t="n"/>
       <c r="O50" s="12" t="n"/>
-      <c r="P50" s="12" t="n"/>
-      <c r="Q50" s="28" t="n"/>
-      <c r="R50" s="12" t="n"/>
+      <c r="P50" s="28" t="n"/>
+      <c r="Q50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -10487,16 +10024,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M51" s="12" t="inlineStr"/>
-      <c r="N51" s="27" t="inlineStr">
+      <c r="M51" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N51" s="12" t="n"/>
       <c r="O51" s="12" t="n"/>
-      <c r="P51" s="12" t="n"/>
-      <c r="Q51" s="28" t="n"/>
-      <c r="R51" s="12" t="n"/>
+      <c r="P51" s="28" t="n"/>
+      <c r="Q51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -10559,16 +10095,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M52" s="12" t="inlineStr"/>
-      <c r="N52" s="27" t="inlineStr">
+      <c r="M52" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N52" s="12" t="n"/>
       <c r="O52" s="12" t="n"/>
-      <c r="P52" s="12" t="n"/>
-      <c r="Q52" s="28" t="n"/>
-      <c r="R52" s="12" t="n"/>
+      <c r="P52" s="28" t="n"/>
+      <c r="Q52" s="12" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -10631,16 +10166,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M53" s="12" t="inlineStr"/>
-      <c r="N53" s="27" t="inlineStr">
+      <c r="M53" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N53" s="12" t="n"/>
       <c r="O53" s="12" t="n"/>
-      <c r="P53" s="12" t="n"/>
-      <c r="Q53" s="28" t="n"/>
-      <c r="R53" s="12" t="n"/>
+      <c r="P53" s="28" t="n"/>
+      <c r="Q53" s="12" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -10703,16 +10237,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M54" s="12" t="inlineStr"/>
-      <c r="N54" s="27" t="inlineStr">
+      <c r="M54" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N54" s="12" t="n"/>
       <c r="O54" s="12" t="n"/>
-      <c r="P54" s="12" t="n"/>
-      <c r="Q54" s="28" t="n"/>
-      <c r="R54" s="12" t="n"/>
+      <c r="P54" s="28" t="n"/>
+      <c r="Q54" s="12" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
@@ -10776,16 +10309,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M55" s="12" t="inlineStr"/>
-      <c r="N55" s="27" t="inlineStr">
+      <c r="M55" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N55" s="12" t="n"/>
       <c r="O55" s="12" t="n"/>
-      <c r="P55" s="12" t="n"/>
-      <c r="Q55" s="28" t="n"/>
-      <c r="R55" s="12" t="n"/>
+      <c r="P55" s="28" t="n"/>
+      <c r="Q55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
@@ -10849,16 +10381,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M56" s="12" t="inlineStr"/>
-      <c r="N56" s="27" t="inlineStr">
+      <c r="M56" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N56" s="12" t="n"/>
       <c r="O56" s="12" t="n"/>
-      <c r="P56" s="12" t="n"/>
-      <c r="Q56" s="28" t="n"/>
-      <c r="R56" s="12" t="n"/>
+      <c r="P56" s="28" t="n"/>
+      <c r="Q56" s="12" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -10921,16 +10452,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M57" s="12" t="inlineStr"/>
-      <c r="N57" s="27" t="inlineStr">
+      <c r="M57" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N57" s="12" t="n"/>
       <c r="O57" s="12" t="n"/>
-      <c r="P57" s="12" t="n"/>
-      <c r="Q57" s="28" t="n"/>
-      <c r="R57" s="12" t="n"/>
+      <c r="P57" s="28" t="n"/>
+      <c r="Q57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
@@ -10993,16 +10523,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M58" s="12" t="inlineStr"/>
-      <c r="N58" s="27" t="inlineStr">
+      <c r="M58" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N58" s="12" t="n"/>
       <c r="O58" s="12" t="n"/>
-      <c r="P58" s="12" t="n"/>
-      <c r="Q58" s="28" t="n"/>
-      <c r="R58" s="12" t="n"/>
+      <c r="P58" s="28" t="n"/>
+      <c r="Q58" s="12" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -11065,16 +10594,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M59" s="12" t="inlineStr"/>
-      <c r="N59" s="27" t="inlineStr">
+      <c r="M59" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N59" s="12" t="n"/>
       <c r="O59" s="12" t="n"/>
-      <c r="P59" s="12" t="n"/>
-      <c r="Q59" s="28" t="n"/>
-      <c r="R59" s="12" t="n"/>
+      <c r="P59" s="28" t="n"/>
+      <c r="Q59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
@@ -11137,16 +10665,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M60" s="12" t="inlineStr"/>
-      <c r="N60" s="27" t="inlineStr">
+      <c r="M60" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N60" s="12" t="n"/>
       <c r="O60" s="12" t="n"/>
-      <c r="P60" s="12" t="n"/>
-      <c r="Q60" s="28" t="n"/>
-      <c r="R60" s="12" t="n"/>
+      <c r="P60" s="28" t="n"/>
+      <c r="Q60" s="12" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -11210,16 +10737,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M61" s="12" t="inlineStr"/>
-      <c r="N61" s="27" t="inlineStr">
+      <c r="M61" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N61" s="12" t="n"/>
       <c r="O61" s="12" t="n"/>
-      <c r="P61" s="12" t="n"/>
-      <c r="Q61" s="28" t="n"/>
-      <c r="R61" s="12" t="n"/>
+      <c r="P61" s="28" t="n"/>
+      <c r="Q61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -11282,16 +10808,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M62" s="12" t="inlineStr"/>
-      <c r="N62" s="27" t="inlineStr">
+      <c r="M62" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N62" s="12" t="n"/>
       <c r="O62" s="12" t="n"/>
-      <c r="P62" s="12" t="n"/>
-      <c r="Q62" s="28" t="n"/>
-      <c r="R62" s="12" t="n"/>
+      <c r="P62" s="28" t="n"/>
+      <c r="Q62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -11354,16 +10879,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M63" s="12" t="inlineStr"/>
-      <c r="N63" s="27" t="inlineStr">
+      <c r="M63" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N63" s="12" t="n"/>
       <c r="O63" s="12" t="n"/>
-      <c r="P63" s="12" t="n"/>
-      <c r="Q63" s="28" t="n"/>
-      <c r="R63" s="12" t="n"/>
+      <c r="P63" s="28" t="n"/>
+      <c r="Q63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
@@ -11427,16 +10951,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M64" s="12" t="inlineStr"/>
-      <c r="N64" s="27" t="inlineStr">
+      <c r="M64" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N64" s="12" t="n"/>
       <c r="O64" s="12" t="n"/>
-      <c r="P64" s="12" t="n"/>
-      <c r="Q64" s="28" t="n"/>
-      <c r="R64" s="12" t="n"/>
+      <c r="P64" s="28" t="n"/>
+      <c r="Q64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -11499,16 +11022,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M65" s="12" t="inlineStr"/>
-      <c r="N65" s="27" t="inlineStr">
+      <c r="M65" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N65" s="12" t="n"/>
       <c r="O65" s="12" t="n"/>
-      <c r="P65" s="12" t="n"/>
-      <c r="Q65" s="28" t="n"/>
-      <c r="R65" s="12" t="n"/>
+      <c r="P65" s="28" t="n"/>
+      <c r="Q65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
@@ -11558,12 +11080,12 @@
       </c>
       <c r="J66" s="12" t="inlineStr">
         <is>
-          <t>1. Open the new-business cycle of Gamma Test Ltd.; call the send endpoint.</t>
+          <t>1. Open the new-business cycle of Gamma Test Ltd.; send a direct send request.</t>
         </is>
       </c>
       <c r="K66" s="12" t="inlineStr">
         <is>
-          <t>The action is not offered; the call is refused.
+          <t>The action is not offered; a direct request is refused.
 Message "The indicative proposal applies to renewals only".</t>
         </is>
       </c>
@@ -11572,16 +11094,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M66" s="12" t="inlineStr"/>
-      <c r="N66" s="27" t="inlineStr">
+      <c r="M66" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N66" s="12" t="n"/>
       <c r="O66" s="12" t="n"/>
-      <c r="P66" s="12" t="n"/>
-      <c r="Q66" s="28" t="n"/>
-      <c r="R66" s="12" t="n"/>
+      <c r="P66" s="28" t="n"/>
+      <c r="Q66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
@@ -11645,16 +11166,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M67" s="12" t="inlineStr"/>
-      <c r="N67" s="27" t="inlineStr">
+      <c r="M67" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N67" s="12" t="n"/>
       <c r="O67" s="12" t="n"/>
-      <c r="P67" s="12" t="n"/>
-      <c r="Q67" s="28" t="n"/>
-      <c r="R67" s="12" t="n"/>
+      <c r="P67" s="28" t="n"/>
+      <c r="Q67" s="12" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
@@ -11717,16 +11237,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M68" s="12" t="inlineStr"/>
-      <c r="N68" s="27" t="inlineStr">
+      <c r="M68" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N68" s="12" t="n"/>
       <c r="O68" s="12" t="n"/>
-      <c r="P68" s="12" t="n"/>
-      <c r="Q68" s="28" t="n"/>
-      <c r="R68" s="12" t="n"/>
+      <c r="P68" s="28" t="n"/>
+      <c r="Q68" s="12" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
@@ -11789,16 +11308,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M69" s="12" t="inlineStr"/>
-      <c r="N69" s="27" t="inlineStr">
+      <c r="M69" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N69" s="12" t="n"/>
       <c r="O69" s="12" t="n"/>
-      <c r="P69" s="12" t="n"/>
-      <c r="Q69" s="28" t="n"/>
-      <c r="R69" s="12" t="n"/>
+      <c r="P69" s="28" t="n"/>
+      <c r="Q69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
@@ -11862,16 +11380,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M70" s="12" t="inlineStr"/>
-      <c r="N70" s="27" t="inlineStr">
+      <c r="M70" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N70" s="12" t="n"/>
       <c r="O70" s="12" t="n"/>
-      <c r="P70" s="12" t="n"/>
-      <c r="Q70" s="28" t="n"/>
-      <c r="R70" s="12" t="n"/>
+      <c r="P70" s="28" t="n"/>
+      <c r="Q70" s="12" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
@@ -11934,16 +11451,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M71" s="12" t="inlineStr"/>
-      <c r="N71" s="27" t="inlineStr">
+      <c r="M71" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N71" s="12" t="n"/>
       <c r="O71" s="12" t="n"/>
-      <c r="P71" s="12" t="n"/>
-      <c r="Q71" s="28" t="n"/>
-      <c r="R71" s="12" t="n"/>
+      <c r="P71" s="28" t="n"/>
+      <c r="Q71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
@@ -12007,16 +11523,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M72" s="12" t="inlineStr"/>
-      <c r="N72" s="27" t="inlineStr">
+      <c r="M72" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N72" s="12" t="n"/>
       <c r="O72" s="12" t="n"/>
-      <c r="P72" s="12" t="n"/>
-      <c r="Q72" s="28" t="n"/>
-      <c r="R72" s="12" t="n"/>
+      <c r="P72" s="28" t="n"/>
+      <c r="Q72" s="12" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
@@ -12079,16 +11594,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M73" s="12" t="inlineStr"/>
-      <c r="N73" s="27" t="inlineStr">
+      <c r="M73" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N73" s="12" t="n"/>
       <c r="O73" s="12" t="n"/>
-      <c r="P73" s="12" t="n"/>
-      <c r="Q73" s="28" t="n"/>
-      <c r="R73" s="12" t="n"/>
+      <c r="P73" s="28" t="n"/>
+      <c r="Q73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
@@ -12152,16 +11666,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M74" s="12" t="inlineStr"/>
-      <c r="N74" s="27" t="inlineStr">
+      <c r="M74" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N74" s="12" t="n"/>
       <c r="O74" s="12" t="n"/>
-      <c r="P74" s="12" t="n"/>
-      <c r="Q74" s="28" t="n"/>
-      <c r="R74" s="12" t="n"/>
+      <c r="P74" s="28" t="n"/>
+      <c r="Q74" s="12" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
@@ -12225,16 +11738,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M75" s="12" t="inlineStr"/>
-      <c r="N75" s="27" t="inlineStr">
+      <c r="M75" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N75" s="12" t="n"/>
       <c r="O75" s="12" t="n"/>
-      <c r="P75" s="12" t="n"/>
-      <c r="Q75" s="28" t="n"/>
-      <c r="R75" s="12" t="n"/>
+      <c r="P75" s="28" t="n"/>
+      <c r="Q75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
@@ -12297,16 +11809,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M76" s="12" t="inlineStr"/>
-      <c r="N76" s="27" t="inlineStr">
+      <c r="M76" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N76" s="12" t="n"/>
       <c r="O76" s="12" t="n"/>
-      <c r="P76" s="12" t="n"/>
-      <c r="Q76" s="28" t="n"/>
-      <c r="R76" s="12" t="n"/>
+      <c r="P76" s="28" t="n"/>
+      <c r="Q76" s="12" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
@@ -12369,16 +11880,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M77" s="12" t="inlineStr"/>
-      <c r="N77" s="27" t="inlineStr">
+      <c r="M77" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N77" s="12" t="n"/>
       <c r="O77" s="12" t="n"/>
-      <c r="P77" s="12" t="n"/>
-      <c r="Q77" s="28" t="n"/>
-      <c r="R77" s="12" t="n"/>
+      <c r="P77" s="28" t="n"/>
+      <c r="Q77" s="12" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
@@ -12442,16 +11952,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M78" s="12" t="inlineStr"/>
-      <c r="N78" s="27" t="inlineStr">
+      <c r="M78" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N78" s="12" t="n"/>
       <c r="O78" s="12" t="n"/>
-      <c r="P78" s="12" t="n"/>
-      <c r="Q78" s="28" t="n"/>
-      <c r="R78" s="12" t="n"/>
+      <c r="P78" s="28" t="n"/>
+      <c r="Q78" s="12" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
@@ -12515,16 +12024,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M79" s="12" t="inlineStr"/>
-      <c r="N79" s="27" t="inlineStr">
+      <c r="M79" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N79" s="12" t="n"/>
       <c r="O79" s="12" t="n"/>
-      <c r="P79" s="12" t="n"/>
-      <c r="Q79" s="28" t="n"/>
-      <c r="R79" s="12" t="n"/>
+      <c r="P79" s="28" t="n"/>
+      <c r="Q79" s="12" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
@@ -12587,16 +12095,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M80" s="12" t="inlineStr"/>
-      <c r="N80" s="27" t="inlineStr">
+      <c r="M80" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N80" s="12" t="n"/>
       <c r="O80" s="12" t="n"/>
-      <c r="P80" s="12" t="n"/>
-      <c r="Q80" s="28" t="n"/>
-      <c r="R80" s="12" t="n"/>
+      <c r="P80" s="28" t="n"/>
+      <c r="Q80" s="12" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
@@ -12659,16 +12166,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M81" s="12" t="inlineStr"/>
-      <c r="N81" s="27" t="inlineStr">
+      <c r="M81" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N81" s="12" t="n"/>
       <c r="O81" s="12" t="n"/>
-      <c r="P81" s="12" t="n"/>
-      <c r="Q81" s="28" t="n"/>
-      <c r="R81" s="12" t="n"/>
+      <c r="P81" s="28" t="n"/>
+      <c r="Q81" s="12" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
@@ -12731,16 +12237,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M82" s="12" t="inlineStr"/>
-      <c r="N82" s="27" t="inlineStr">
+      <c r="M82" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N82" s="12" t="n"/>
       <c r="O82" s="12" t="n"/>
-      <c r="P82" s="12" t="n"/>
-      <c r="Q82" s="28" t="n"/>
-      <c r="R82" s="12" t="n"/>
+      <c r="P82" s="28" t="n"/>
+      <c r="Q82" s="12" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
@@ -12804,16 +12309,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M83" s="12" t="inlineStr"/>
-      <c r="N83" s="27" t="inlineStr">
+      <c r="M83" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N83" s="12" t="n"/>
       <c r="O83" s="12" t="n"/>
-      <c r="P83" s="12" t="n"/>
-      <c r="Q83" s="28" t="n"/>
-      <c r="R83" s="12" t="n"/>
+      <c r="P83" s="28" t="n"/>
+      <c r="Q83" s="12" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
@@ -12876,16 +12380,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M84" s="12" t="inlineStr"/>
-      <c r="N84" s="27" t="inlineStr">
+      <c r="M84" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N84" s="12" t="n"/>
       <c r="O84" s="12" t="n"/>
-      <c r="P84" s="12" t="n"/>
-      <c r="Q84" s="28" t="n"/>
-      <c r="R84" s="12" t="n"/>
+      <c r="P84" s="28" t="n"/>
+      <c r="Q84" s="12" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
@@ -12948,16 +12451,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M85" s="12" t="inlineStr"/>
-      <c r="N85" s="27" t="inlineStr">
+      <c r="M85" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N85" s="12" t="n"/>
       <c r="O85" s="12" t="n"/>
-      <c r="P85" s="12" t="n"/>
-      <c r="Q85" s="28" t="n"/>
-      <c r="R85" s="12" t="n"/>
+      <c r="P85" s="28" t="n"/>
+      <c r="Q85" s="12" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
@@ -13021,16 +12523,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M86" s="12" t="inlineStr"/>
-      <c r="N86" s="27" t="inlineStr">
+      <c r="M86" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N86" s="12" t="n"/>
       <c r="O86" s="12" t="n"/>
-      <c r="P86" s="12" t="n"/>
-      <c r="Q86" s="28" t="n"/>
-      <c r="R86" s="12" t="n"/>
+      <c r="P86" s="28" t="n"/>
+      <c r="Q86" s="12" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
@@ -13093,16 +12594,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M87" s="12" t="inlineStr"/>
-      <c r="N87" s="27" t="inlineStr">
+      <c r="M87" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N87" s="12" t="n"/>
       <c r="O87" s="12" t="n"/>
-      <c r="P87" s="12" t="n"/>
-      <c r="Q87" s="28" t="n"/>
-      <c r="R87" s="12" t="n"/>
+      <c r="P87" s="28" t="n"/>
+      <c r="Q87" s="12" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
@@ -13157,7 +12657,7 @@
       </c>
       <c r="K88" s="12" t="inlineStr">
         <is>
-          <t>The insurer cannot be selected; the API call is refused.
+          <t>The insurer cannot be selected; the direct request is refused.
 Message "Insurer INS-D has no approved franchise for this cycle".</t>
         </is>
       </c>
@@ -13166,16 +12666,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M88" s="12" t="inlineStr"/>
-      <c r="N88" s="27" t="inlineStr">
+      <c r="M88" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N88" s="12" t="n"/>
       <c r="O88" s="12" t="n"/>
-      <c r="P88" s="12" t="n"/>
-      <c r="Q88" s="28" t="n"/>
-      <c r="R88" s="12" t="n"/>
+      <c r="P88" s="28" t="n"/>
+      <c r="Q88" s="12" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
@@ -13238,16 +12737,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M89" s="12" t="inlineStr"/>
-      <c r="N89" s="27" t="inlineStr">
+      <c r="M89" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N89" s="12" t="n"/>
       <c r="O89" s="12" t="n"/>
-      <c r="P89" s="12" t="n"/>
-      <c r="Q89" s="28" t="n"/>
-      <c r="R89" s="12" t="n"/>
+      <c r="P89" s="28" t="n"/>
+      <c r="Q89" s="12" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
@@ -13310,16 +12808,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M90" s="12" t="inlineStr"/>
-      <c r="N90" s="27" t="inlineStr">
+      <c r="M90" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N90" s="12" t="n"/>
       <c r="O90" s="12" t="n"/>
-      <c r="P90" s="12" t="n"/>
-      <c r="Q90" s="28" t="n"/>
-      <c r="R90" s="12" t="n"/>
+      <c r="P90" s="28" t="n"/>
+      <c r="Q90" s="12" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
@@ -13383,16 +12880,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M91" s="12" t="inlineStr"/>
-      <c r="N91" s="27" t="inlineStr">
+      <c r="M91" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N91" s="12" t="n"/>
       <c r="O91" s="12" t="n"/>
-      <c r="P91" s="12" t="n"/>
-      <c r="Q91" s="28" t="n"/>
-      <c r="R91" s="12" t="n"/>
+      <c r="P91" s="28" t="n"/>
+      <c r="Q91" s="12" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
@@ -13455,16 +12951,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M92" s="12" t="inlineStr"/>
-      <c r="N92" s="27" t="inlineStr">
+      <c r="M92" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N92" s="12" t="n"/>
       <c r="O92" s="12" t="n"/>
-      <c r="P92" s="12" t="n"/>
-      <c r="Q92" s="28" t="n"/>
-      <c r="R92" s="12" t="n"/>
+      <c r="P92" s="28" t="n"/>
+      <c r="Q92" s="12" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
@@ -13514,7 +13009,7 @@
       </c>
       <c r="J93" s="12" t="inlineStr">
         <is>
-          <t>1. Build the comparative while the INS-A proposal is still SUBMITTED.</t>
+          <t>1. Click Build Comparative while the INS-A proposal is still SUBMITTED.</t>
         </is>
       </c>
       <c r="K93" s="12" t="inlineStr">
@@ -13527,16 +13022,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M93" s="12" t="inlineStr"/>
-      <c r="N93" s="27" t="inlineStr">
+      <c r="M93" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N93" s="12" t="n"/>
       <c r="O93" s="12" t="n"/>
-      <c r="P93" s="12" t="n"/>
-      <c r="Q93" s="28" t="n"/>
-      <c r="R93" s="12" t="n"/>
+      <c r="P93" s="28" t="n"/>
+      <c r="Q93" s="12" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
@@ -13600,16 +13094,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M94" s="12" t="inlineStr"/>
-      <c r="N94" s="27" t="inlineStr">
+      <c r="M94" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N94" s="12" t="n"/>
       <c r="O94" s="12" t="n"/>
-      <c r="P94" s="12" t="n"/>
-      <c r="Q94" s="28" t="n"/>
-      <c r="R94" s="12" t="n"/>
+      <c r="P94" s="28" t="n"/>
+      <c r="Q94" s="12" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
@@ -13673,16 +13166,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M95" s="12" t="inlineStr"/>
-      <c r="N95" s="27" t="inlineStr">
+      <c r="M95" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N95" s="12" t="n"/>
       <c r="O95" s="12" t="n"/>
-      <c r="P95" s="12" t="n"/>
-      <c r="Q95" s="28" t="n"/>
-      <c r="R95" s="12" t="n"/>
+      <c r="P95" s="28" t="n"/>
+      <c r="Q95" s="12" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
@@ -13745,16 +13237,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M96" s="12" t="inlineStr"/>
-      <c r="N96" s="27" t="inlineStr">
+      <c r="M96" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N96" s="12" t="n"/>
       <c r="O96" s="12" t="n"/>
-      <c r="P96" s="12" t="n"/>
-      <c r="Q96" s="28" t="n"/>
-      <c r="R96" s="12" t="n"/>
+      <c r="P96" s="28" t="n"/>
+      <c r="Q96" s="12" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
@@ -13817,16 +13308,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M97" s="12" t="inlineStr"/>
-      <c r="N97" s="27" t="inlineStr">
+      <c r="M97" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N97" s="12" t="n"/>
       <c r="O97" s="12" t="n"/>
-      <c r="P97" s="12" t="n"/>
-      <c r="Q97" s="28" t="n"/>
-      <c r="R97" s="12" t="n"/>
+      <c r="P97" s="28" t="n"/>
+      <c r="Q97" s="12" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
@@ -13876,7 +13366,7 @@
       </c>
       <c r="J98" s="12" t="inlineStr">
         <is>
-          <t>1. Build the comparative while one insurer request is open.</t>
+          <t>1. Click Build Comparative while one insurer request is open.</t>
         </is>
       </c>
       <c r="K98" s="12" t="inlineStr">
@@ -13890,16 +13380,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M98" s="12" t="inlineStr"/>
-      <c r="N98" s="27" t="inlineStr">
+      <c r="M98" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N98" s="12" t="n"/>
       <c r="O98" s="12" t="n"/>
-      <c r="P98" s="12" t="n"/>
-      <c r="Q98" s="28" t="n"/>
-      <c r="R98" s="12" t="n"/>
+      <c r="P98" s="28" t="n"/>
+      <c r="Q98" s="12" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
@@ -13963,16 +13452,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M99" s="12" t="inlineStr"/>
-      <c r="N99" s="27" t="inlineStr">
+      <c r="M99" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N99" s="12" t="n"/>
       <c r="O99" s="12" t="n"/>
-      <c r="P99" s="12" t="n"/>
-      <c r="Q99" s="28" t="n"/>
-      <c r="R99" s="12" t="n"/>
+      <c r="P99" s="28" t="n"/>
+      <c r="Q99" s="12" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
@@ -14036,16 +13524,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M100" s="12" t="inlineStr"/>
-      <c r="N100" s="27" t="inlineStr">
+      <c r="M100" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N100" s="12" t="n"/>
       <c r="O100" s="12" t="n"/>
-      <c r="P100" s="12" t="n"/>
-      <c r="Q100" s="28" t="n"/>
-      <c r="R100" s="12" t="n"/>
+      <c r="P100" s="28" t="n"/>
+      <c r="Q100" s="12" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
@@ -14108,16 +13595,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M101" s="12" t="inlineStr"/>
-      <c r="N101" s="27" t="inlineStr">
+      <c r="M101" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N101" s="12" t="n"/>
       <c r="O101" s="12" t="n"/>
-      <c r="P101" s="12" t="n"/>
-      <c r="Q101" s="28" t="n"/>
-      <c r="R101" s="12" t="n"/>
+      <c r="P101" s="28" t="n"/>
+      <c r="Q101" s="12" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
@@ -14180,16 +13666,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M102" s="12" t="inlineStr"/>
-      <c r="N102" s="27" t="inlineStr">
+      <c r="M102" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N102" s="12" t="n"/>
       <c r="O102" s="12" t="n"/>
-      <c r="P102" s="12" t="n"/>
-      <c r="Q102" s="28" t="n"/>
-      <c r="R102" s="12" t="n"/>
+      <c r="P102" s="28" t="n"/>
+      <c r="Q102" s="12" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
@@ -14253,16 +13738,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M103" s="12" t="inlineStr"/>
-      <c r="N103" s="27" t="inlineStr">
+      <c r="M103" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N103" s="12" t="n"/>
       <c r="O103" s="12" t="n"/>
-      <c r="P103" s="12" t="n"/>
-      <c r="Q103" s="28" t="n"/>
-      <c r="R103" s="12" t="n"/>
+      <c r="P103" s="28" t="n"/>
+      <c r="Q103" s="12" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
@@ -14325,16 +13809,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M104" s="12" t="inlineStr"/>
-      <c r="N104" s="27" t="inlineStr">
+      <c r="M104" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N104" s="12" t="n"/>
       <c r="O104" s="12" t="n"/>
-      <c r="P104" s="12" t="n"/>
-      <c r="Q104" s="28" t="n"/>
-      <c r="R104" s="12" t="n"/>
+      <c r="P104" s="28" t="n"/>
+      <c r="Q104" s="12" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
@@ -14397,16 +13880,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M105" s="12" t="inlineStr"/>
-      <c r="N105" s="27" t="inlineStr">
+      <c r="M105" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N105" s="12" t="n"/>
       <c r="O105" s="12" t="n"/>
-      <c r="P105" s="12" t="n"/>
-      <c r="Q105" s="28" t="n"/>
-      <c r="R105" s="12" t="n"/>
+      <c r="P105" s="28" t="n"/>
+      <c r="Q105" s="12" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
@@ -14470,16 +13952,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M106" s="12" t="inlineStr"/>
-      <c r="N106" s="27" t="inlineStr">
+      <c r="M106" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N106" s="12" t="n"/>
       <c r="O106" s="12" t="n"/>
-      <c r="P106" s="12" t="n"/>
-      <c r="Q106" s="28" t="n"/>
-      <c r="R106" s="12" t="n"/>
+      <c r="P106" s="28" t="n"/>
+      <c r="Q106" s="12" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
@@ -14542,16 +14023,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M107" s="12" t="inlineStr"/>
-      <c r="N107" s="27" t="inlineStr">
+      <c r="M107" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N107" s="12" t="n"/>
       <c r="O107" s="12" t="n"/>
-      <c r="P107" s="12" t="n"/>
-      <c r="Q107" s="28" t="n"/>
-      <c r="R107" s="12" t="n"/>
+      <c r="P107" s="28" t="n"/>
+      <c r="Q107" s="12" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
@@ -14614,16 +14094,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M108" s="12" t="inlineStr"/>
-      <c r="N108" s="27" t="inlineStr">
+      <c r="M108" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N108" s="12" t="n"/>
       <c r="O108" s="12" t="n"/>
-      <c r="P108" s="12" t="n"/>
-      <c r="Q108" s="28" t="n"/>
-      <c r="R108" s="12" t="n"/>
+      <c r="P108" s="28" t="n"/>
+      <c r="Q108" s="12" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
@@ -14687,16 +14166,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M109" s="12" t="inlineStr"/>
-      <c r="N109" s="27" t="inlineStr">
+      <c r="M109" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N109" s="12" t="n"/>
       <c r="O109" s="12" t="n"/>
-      <c r="P109" s="12" t="n"/>
-      <c r="Q109" s="28" t="n"/>
-      <c r="R109" s="12" t="n"/>
+      <c r="P109" s="28" t="n"/>
+      <c r="Q109" s="12" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
@@ -14751,7 +14229,7 @@
       </c>
       <c r="K110" s="12" t="inlineStr">
         <is>
-          <t>The action is not offered; the call is refused.</t>
+          <t>The action is not offered; a direct request is refused.</t>
         </is>
       </c>
       <c r="L110" s="12" t="inlineStr">
@@ -14759,16 +14237,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M110" s="12" t="inlineStr"/>
-      <c r="N110" s="27" t="inlineStr">
+      <c r="M110" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N110" s="12" t="n"/>
       <c r="O110" s="12" t="n"/>
-      <c r="P110" s="12" t="n"/>
-      <c r="Q110" s="28" t="n"/>
-      <c r="R110" s="12" t="n"/>
+      <c r="P110" s="28" t="n"/>
+      <c r="Q110" s="12" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
@@ -14831,16 +14308,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M111" s="12" t="inlineStr"/>
-      <c r="N111" s="27" t="inlineStr">
+      <c r="M111" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N111" s="12" t="n"/>
       <c r="O111" s="12" t="n"/>
-      <c r="P111" s="12" t="n"/>
-      <c r="Q111" s="28" t="n"/>
-      <c r="R111" s="12" t="n"/>
+      <c r="P111" s="28" t="n"/>
+      <c r="Q111" s="12" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
@@ -14904,16 +14380,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M112" s="12" t="inlineStr"/>
-      <c r="N112" s="27" t="inlineStr">
+      <c r="M112" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N112" s="12" t="n"/>
       <c r="O112" s="12" t="n"/>
-      <c r="P112" s="12" t="n"/>
-      <c r="Q112" s="28" t="n"/>
-      <c r="R112" s="12" t="n"/>
+      <c r="P112" s="28" t="n"/>
+      <c r="Q112" s="12" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
@@ -14977,16 +14452,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M113" s="12" t="inlineStr"/>
-      <c r="N113" s="27" t="inlineStr">
+      <c r="M113" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N113" s="12" t="n"/>
       <c r="O113" s="12" t="n"/>
-      <c r="P113" s="12" t="n"/>
-      <c r="Q113" s="28" t="n"/>
-      <c r="R113" s="12" t="n"/>
+      <c r="P113" s="28" t="n"/>
+      <c r="Q113" s="12" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
@@ -15050,16 +14524,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M114" s="12" t="inlineStr"/>
-      <c r="N114" s="27" t="inlineStr">
+      <c r="M114" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N114" s="12" t="n"/>
       <c r="O114" s="12" t="n"/>
-      <c r="P114" s="12" t="n"/>
-      <c r="Q114" s="28" t="n"/>
-      <c r="R114" s="12" t="n"/>
+      <c r="P114" s="28" t="n"/>
+      <c r="Q114" s="12" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="12" t="inlineStr">
@@ -15123,16 +14596,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M115" s="12" t="inlineStr"/>
-      <c r="N115" s="27" t="inlineStr">
+      <c r="M115" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N115" s="12" t="n"/>
       <c r="O115" s="12" t="n"/>
-      <c r="P115" s="12" t="n"/>
-      <c r="Q115" s="28" t="n"/>
-      <c r="R115" s="12" t="n"/>
+      <c r="P115" s="28" t="n"/>
+      <c r="Q115" s="12" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
@@ -15196,16 +14668,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M116" s="12" t="inlineStr"/>
-      <c r="N116" s="27" t="inlineStr">
+      <c r="M116" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N116" s="12" t="n"/>
       <c r="O116" s="12" t="n"/>
-      <c r="P116" s="12" t="n"/>
-      <c r="Q116" s="28" t="n"/>
-      <c r="R116" s="12" t="n"/>
+      <c r="P116" s="28" t="n"/>
+      <c r="Q116" s="12" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="12" t="inlineStr">
@@ -15268,16 +14739,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M117" s="12" t="inlineStr"/>
-      <c r="N117" s="27" t="inlineStr">
+      <c r="M117" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N117" s="12" t="n"/>
       <c r="O117" s="12" t="n"/>
-      <c r="P117" s="12" t="n"/>
-      <c r="Q117" s="28" t="n"/>
-      <c r="R117" s="12" t="n"/>
+      <c r="P117" s="28" t="n"/>
+      <c r="Q117" s="12" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
@@ -15340,16 +14810,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M118" s="12" t="inlineStr"/>
-      <c r="N118" s="27" t="inlineStr">
+      <c r="M118" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N118" s="12" t="n"/>
       <c r="O118" s="12" t="n"/>
-      <c r="P118" s="12" t="n"/>
-      <c r="Q118" s="28" t="n"/>
-      <c r="R118" s="12" t="n"/>
+      <c r="P118" s="28" t="n"/>
+      <c r="Q118" s="12" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="12" t="inlineStr">
@@ -15414,16 +14883,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M119" s="12" t="inlineStr"/>
-      <c r="N119" s="27" t="inlineStr">
+      <c r="M119" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N119" s="12" t="n"/>
       <c r="O119" s="12" t="n"/>
-      <c r="P119" s="12" t="n"/>
-      <c r="Q119" s="28" t="n"/>
-      <c r="R119" s="12" t="n"/>
+      <c r="P119" s="28" t="n"/>
+      <c r="Q119" s="12" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
@@ -15486,16 +14954,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M120" s="12" t="inlineStr"/>
-      <c r="N120" s="27" t="inlineStr">
+      <c r="M120" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N120" s="12" t="n"/>
       <c r="O120" s="12" t="n"/>
-      <c r="P120" s="12" t="n"/>
-      <c r="Q120" s="28" t="n"/>
-      <c r="R120" s="12" t="n"/>
+      <c r="P120" s="28" t="n"/>
+      <c r="Q120" s="12" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="12" t="inlineStr">
@@ -15558,16 +15025,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M121" s="12" t="inlineStr"/>
-      <c r="N121" s="27" t="inlineStr">
+      <c r="M121" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N121" s="12" t="n"/>
       <c r="O121" s="12" t="n"/>
-      <c r="P121" s="12" t="n"/>
-      <c r="Q121" s="28" t="n"/>
-      <c r="R121" s="12" t="n"/>
+      <c r="P121" s="28" t="n"/>
+      <c r="Q121" s="12" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="12" t="inlineStr">
@@ -15630,16 +15096,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M122" s="12" t="inlineStr"/>
-      <c r="N122" s="27" t="inlineStr">
+      <c r="M122" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N122" s="12" t="n"/>
       <c r="O122" s="12" t="n"/>
-      <c r="P122" s="12" t="n"/>
-      <c r="Q122" s="28" t="n"/>
-      <c r="R122" s="12" t="n"/>
+      <c r="P122" s="28" t="n"/>
+      <c r="Q122" s="12" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="12" t="inlineStr">
@@ -15703,16 +15168,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M123" s="12" t="inlineStr"/>
-      <c r="N123" s="27" t="inlineStr">
+      <c r="M123" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N123" s="12" t="n"/>
       <c r="O123" s="12" t="n"/>
-      <c r="P123" s="12" t="n"/>
-      <c r="Q123" s="28" t="n"/>
-      <c r="R123" s="12" t="n"/>
+      <c r="P123" s="28" t="n"/>
+      <c r="Q123" s="12" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="12" t="inlineStr">
@@ -15775,16 +15239,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M124" s="12" t="inlineStr"/>
-      <c r="N124" s="27" t="inlineStr">
+      <c r="M124" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N124" s="12" t="n"/>
       <c r="O124" s="12" t="n"/>
-      <c r="P124" s="12" t="n"/>
-      <c r="Q124" s="28" t="n"/>
-      <c r="R124" s="12" t="n"/>
+      <c r="P124" s="28" t="n"/>
+      <c r="Q124" s="12" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="12" t="inlineStr">
@@ -15847,16 +15310,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M125" s="12" t="inlineStr"/>
-      <c r="N125" s="27" t="inlineStr">
+      <c r="M125" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N125" s="12" t="n"/>
       <c r="O125" s="12" t="n"/>
-      <c r="P125" s="12" t="n"/>
-      <c r="Q125" s="28" t="n"/>
-      <c r="R125" s="12" t="n"/>
+      <c r="P125" s="28" t="n"/>
+      <c r="Q125" s="12" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="12" t="inlineStr">
@@ -15919,16 +15381,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M126" s="12" t="inlineStr"/>
-      <c r="N126" s="27" t="inlineStr">
+      <c r="M126" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N126" s="12" t="n"/>
       <c r="O126" s="12" t="n"/>
-      <c r="P126" s="12" t="n"/>
-      <c r="Q126" s="28" t="n"/>
-      <c r="R126" s="12" t="n"/>
+      <c r="P126" s="28" t="n"/>
+      <c r="Q126" s="12" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="12" t="inlineStr">
@@ -15992,16 +15453,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M127" s="12" t="inlineStr"/>
-      <c r="N127" s="27" t="inlineStr">
+      <c r="M127" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N127" s="12" t="n"/>
       <c r="O127" s="12" t="n"/>
-      <c r="P127" s="12" t="n"/>
-      <c r="Q127" s="28" t="n"/>
-      <c r="R127" s="12" t="n"/>
+      <c r="P127" s="28" t="n"/>
+      <c r="Q127" s="12" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="12" t="inlineStr">
@@ -16064,16 +15524,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M128" s="12" t="inlineStr"/>
-      <c r="N128" s="27" t="inlineStr">
+      <c r="M128" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N128" s="12" t="n"/>
       <c r="O128" s="12" t="n"/>
-      <c r="P128" s="12" t="n"/>
-      <c r="Q128" s="28" t="n"/>
-      <c r="R128" s="12" t="n"/>
+      <c r="P128" s="28" t="n"/>
+      <c r="Q128" s="12" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="12" t="inlineStr">
@@ -16137,16 +15596,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M129" s="12" t="inlineStr"/>
-      <c r="N129" s="27" t="inlineStr">
+      <c r="M129" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N129" s="12" t="n"/>
       <c r="O129" s="12" t="n"/>
-      <c r="P129" s="12" t="n"/>
-      <c r="Q129" s="28" t="n"/>
-      <c r="R129" s="12" t="n"/>
+      <c r="P129" s="28" t="n"/>
+      <c r="Q129" s="12" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="12" t="inlineStr">
@@ -16209,16 +15667,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M130" s="12" t="inlineStr"/>
-      <c r="N130" s="27" t="inlineStr">
+      <c r="M130" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N130" s="12" t="n"/>
       <c r="O130" s="12" t="n"/>
-      <c r="P130" s="12" t="n"/>
-      <c r="Q130" s="28" t="n"/>
-      <c r="R130" s="12" t="n"/>
+      <c r="P130" s="28" t="n"/>
+      <c r="Q130" s="12" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="12" t="inlineStr">
@@ -16282,16 +15739,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M131" s="12" t="inlineStr"/>
-      <c r="N131" s="27" t="inlineStr">
+      <c r="M131" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N131" s="12" t="n"/>
       <c r="O131" s="12" t="n"/>
-      <c r="P131" s="12" t="n"/>
-      <c r="Q131" s="28" t="n"/>
-      <c r="R131" s="12" t="n"/>
+      <c r="P131" s="28" t="n"/>
+      <c r="Q131" s="12" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="12" t="inlineStr">
@@ -16355,16 +15811,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M132" s="12" t="inlineStr"/>
-      <c r="N132" s="27" t="inlineStr">
+      <c r="M132" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N132" s="12" t="n"/>
       <c r="O132" s="12" t="n"/>
-      <c r="P132" s="12" t="n"/>
-      <c r="Q132" s="28" t="n"/>
-      <c r="R132" s="12" t="n"/>
+      <c r="P132" s="28" t="n"/>
+      <c r="Q132" s="12" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="12" t="inlineStr">
@@ -16427,16 +15882,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M133" s="12" t="inlineStr"/>
-      <c r="N133" s="27" t="inlineStr">
+      <c r="M133" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N133" s="12" t="n"/>
       <c r="O133" s="12" t="n"/>
-      <c r="P133" s="12" t="n"/>
-      <c r="Q133" s="28" t="n"/>
-      <c r="R133" s="12" t="n"/>
+      <c r="P133" s="28" t="n"/>
+      <c r="Q133" s="12" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="12" t="inlineStr">
@@ -16499,16 +15953,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M134" s="12" t="inlineStr"/>
-      <c r="N134" s="27" t="inlineStr">
+      <c r="M134" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N134" s="12" t="n"/>
       <c r="O134" s="12" t="n"/>
-      <c r="P134" s="12" t="n"/>
-      <c r="Q134" s="28" t="n"/>
-      <c r="R134" s="12" t="n"/>
+      <c r="P134" s="28" t="n"/>
+      <c r="Q134" s="12" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="12" t="inlineStr">
@@ -16572,16 +16025,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M135" s="12" t="inlineStr"/>
-      <c r="N135" s="27" t="inlineStr">
+      <c r="M135" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N135" s="12" t="n"/>
       <c r="O135" s="12" t="n"/>
-      <c r="P135" s="12" t="n"/>
-      <c r="Q135" s="28" t="n"/>
-      <c r="R135" s="12" t="n"/>
+      <c r="P135" s="28" t="n"/>
+      <c r="Q135" s="12" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="12" t="inlineStr">
@@ -16644,16 +16096,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M136" s="12" t="inlineStr"/>
-      <c r="N136" s="27" t="inlineStr">
+      <c r="M136" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N136" s="12" t="n"/>
       <c r="O136" s="12" t="n"/>
-      <c r="P136" s="12" t="n"/>
-      <c r="Q136" s="28" t="n"/>
-      <c r="R136" s="12" t="n"/>
+      <c r="P136" s="28" t="n"/>
+      <c r="Q136" s="12" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="12" t="inlineStr">
@@ -16716,16 +16167,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M137" s="12" t="inlineStr"/>
-      <c r="N137" s="27" t="inlineStr">
+      <c r="M137" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N137" s="12" t="n"/>
       <c r="O137" s="12" t="n"/>
-      <c r="P137" s="12" t="n"/>
-      <c r="Q137" s="28" t="n"/>
-      <c r="R137" s="12" t="n"/>
+      <c r="P137" s="28" t="n"/>
+      <c r="Q137" s="12" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="12" t="inlineStr">
@@ -16788,16 +16238,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M138" s="12" t="inlineStr"/>
-      <c r="N138" s="27" t="inlineStr">
+      <c r="M138" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N138" s="12" t="n"/>
       <c r="O138" s="12" t="n"/>
-      <c r="P138" s="12" t="n"/>
-      <c r="Q138" s="28" t="n"/>
-      <c r="R138" s="12" t="n"/>
+      <c r="P138" s="28" t="n"/>
+      <c r="Q138" s="12" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="12" t="inlineStr">
@@ -16861,16 +16310,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M139" s="12" t="inlineStr"/>
-      <c r="N139" s="27" t="inlineStr">
+      <c r="M139" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N139" s="12" t="n"/>
       <c r="O139" s="12" t="n"/>
-      <c r="P139" s="12" t="n"/>
-      <c r="Q139" s="28" t="n"/>
-      <c r="R139" s="12" t="n"/>
+      <c r="P139" s="28" t="n"/>
+      <c r="Q139" s="12" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="12" t="inlineStr">
@@ -16934,16 +16382,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M140" s="12" t="inlineStr"/>
-      <c r="N140" s="27" t="inlineStr">
+      <c r="M140" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N140" s="12" t="n"/>
       <c r="O140" s="12" t="n"/>
-      <c r="P140" s="12" t="n"/>
-      <c r="Q140" s="28" t="n"/>
-      <c r="R140" s="12" t="n"/>
+      <c r="P140" s="28" t="n"/>
+      <c r="Q140" s="12" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="12" t="inlineStr">
@@ -17006,16 +16453,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M141" s="12" t="inlineStr"/>
-      <c r="N141" s="27" t="inlineStr">
+      <c r="M141" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N141" s="12" t="n"/>
       <c r="O141" s="12" t="n"/>
-      <c r="P141" s="12" t="n"/>
-      <c r="Q141" s="28" t="n"/>
-      <c r="R141" s="12" t="n"/>
+      <c r="P141" s="28" t="n"/>
+      <c r="Q141" s="12" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="12" t="inlineStr">
@@ -17079,16 +16525,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M142" s="12" t="inlineStr"/>
-      <c r="N142" s="27" t="inlineStr">
+      <c r="M142" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N142" s="12" t="n"/>
       <c r="O142" s="12" t="n"/>
-      <c r="P142" s="12" t="n"/>
-      <c r="Q142" s="28" t="n"/>
-      <c r="R142" s="12" t="n"/>
+      <c r="P142" s="28" t="n"/>
+      <c r="Q142" s="12" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="12" t="inlineStr">
@@ -17151,16 +16596,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M143" s="12" t="inlineStr"/>
-      <c r="N143" s="27" t="inlineStr">
+      <c r="M143" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N143" s="12" t="n"/>
       <c r="O143" s="12" t="n"/>
-      <c r="P143" s="12" t="n"/>
-      <c r="Q143" s="28" t="n"/>
-      <c r="R143" s="12" t="n"/>
+      <c r="P143" s="28" t="n"/>
+      <c r="Q143" s="12" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="12" t="inlineStr">
@@ -17223,16 +16667,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M144" s="12" t="inlineStr"/>
-      <c r="N144" s="27" t="inlineStr">
+      <c r="M144" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N144" s="12" t="n"/>
       <c r="O144" s="12" t="n"/>
-      <c r="P144" s="12" t="n"/>
-      <c r="Q144" s="28" t="n"/>
-      <c r="R144" s="12" t="n"/>
+      <c r="P144" s="28" t="n"/>
+      <c r="Q144" s="12" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="12" t="inlineStr">
@@ -17295,16 +16738,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M145" s="12" t="inlineStr"/>
-      <c r="N145" s="27" t="inlineStr">
+      <c r="M145" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N145" s="12" t="n"/>
       <c r="O145" s="12" t="n"/>
-      <c r="P145" s="12" t="n"/>
-      <c r="Q145" s="28" t="n"/>
-      <c r="R145" s="12" t="n"/>
+      <c r="P145" s="28" t="n"/>
+      <c r="Q145" s="12" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="12" t="inlineStr">
@@ -17368,16 +16810,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M146" s="12" t="inlineStr"/>
-      <c r="N146" s="27" t="inlineStr">
+      <c r="M146" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N146" s="12" t="n"/>
       <c r="O146" s="12" t="n"/>
-      <c r="P146" s="12" t="n"/>
-      <c r="Q146" s="28" t="n"/>
-      <c r="R146" s="12" t="n"/>
+      <c r="P146" s="28" t="n"/>
+      <c r="Q146" s="12" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="12" t="inlineStr">
@@ -17440,16 +16881,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M147" s="12" t="inlineStr"/>
-      <c r="N147" s="27" t="inlineStr">
+      <c r="M147" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N147" s="12" t="n"/>
       <c r="O147" s="12" t="n"/>
-      <c r="P147" s="12" t="n"/>
-      <c r="Q147" s="28" t="n"/>
-      <c r="R147" s="12" t="n"/>
+      <c r="P147" s="28" t="n"/>
+      <c r="Q147" s="12" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="12" t="inlineStr">
@@ -17512,16 +16952,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M148" s="12" t="inlineStr"/>
-      <c r="N148" s="27" t="inlineStr">
+      <c r="M148" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N148" s="12" t="n"/>
       <c r="O148" s="12" t="n"/>
-      <c r="P148" s="12" t="n"/>
-      <c r="Q148" s="28" t="n"/>
-      <c r="R148" s="12" t="n"/>
+      <c r="P148" s="28" t="n"/>
+      <c r="Q148" s="12" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="12" t="inlineStr">
@@ -17584,16 +17023,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M149" s="12" t="inlineStr"/>
-      <c r="N149" s="27" t="inlineStr">
+      <c r="M149" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N149" s="12" t="n"/>
       <c r="O149" s="12" t="n"/>
-      <c r="P149" s="12" t="n"/>
-      <c r="Q149" s="28" t="n"/>
-      <c r="R149" s="12" t="n"/>
+      <c r="P149" s="28" t="n"/>
+      <c r="Q149" s="12" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="12" t="inlineStr">
@@ -17657,16 +17095,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M150" s="12" t="inlineStr"/>
-      <c r="N150" s="27" t="inlineStr">
+      <c r="M150" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N150" s="12" t="n"/>
       <c r="O150" s="12" t="n"/>
-      <c r="P150" s="12" t="n"/>
-      <c r="Q150" s="28" t="n"/>
-      <c r="R150" s="12" t="n"/>
+      <c r="P150" s="28" t="n"/>
+      <c r="Q150" s="12" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="12" t="inlineStr">
@@ -17729,16 +17166,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M151" s="12" t="inlineStr"/>
-      <c r="N151" s="27" t="inlineStr">
+      <c r="M151" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N151" s="12" t="n"/>
       <c r="O151" s="12" t="n"/>
-      <c r="P151" s="12" t="n"/>
-      <c r="Q151" s="28" t="n"/>
-      <c r="R151" s="12" t="n"/>
+      <c r="P151" s="28" t="n"/>
+      <c r="Q151" s="12" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="12" t="inlineStr">
@@ -17801,16 +17237,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M152" s="12" t="inlineStr"/>
-      <c r="N152" s="27" t="inlineStr">
+      <c r="M152" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N152" s="12" t="n"/>
       <c r="O152" s="12" t="n"/>
-      <c r="P152" s="12" t="n"/>
-      <c r="Q152" s="28" t="n"/>
-      <c r="R152" s="12" t="n"/>
+      <c r="P152" s="28" t="n"/>
+      <c r="Q152" s="12" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="12" t="inlineStr">
@@ -17873,16 +17308,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M153" s="12" t="inlineStr"/>
-      <c r="N153" s="27" t="inlineStr">
+      <c r="M153" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N153" s="12" t="n"/>
       <c r="O153" s="12" t="n"/>
-      <c r="P153" s="12" t="n"/>
-      <c r="Q153" s="28" t="n"/>
-      <c r="R153" s="12" t="n"/>
+      <c r="P153" s="28" t="n"/>
+      <c r="Q153" s="12" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="12" t="inlineStr">
@@ -17946,16 +17380,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M154" s="12" t="inlineStr"/>
-      <c r="N154" s="27" t="inlineStr">
+      <c r="M154" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N154" s="12" t="n"/>
       <c r="O154" s="12" t="n"/>
-      <c r="P154" s="12" t="n"/>
-      <c r="Q154" s="28" t="n"/>
-      <c r="R154" s="12" t="n"/>
+      <c r="P154" s="28" t="n"/>
+      <c r="Q154" s="12" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="12" t="inlineStr">
@@ -18018,16 +17451,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M155" s="12" t="inlineStr"/>
-      <c r="N155" s="27" t="inlineStr">
+      <c r="M155" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N155" s="12" t="n"/>
       <c r="O155" s="12" t="n"/>
-      <c r="P155" s="12" t="n"/>
-      <c r="Q155" s="28" t="n"/>
-      <c r="R155" s="12" t="n"/>
+      <c r="P155" s="28" t="n"/>
+      <c r="Q155" s="12" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="12" t="inlineStr">
@@ -18090,16 +17522,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M156" s="12" t="inlineStr"/>
-      <c r="N156" s="27" t="inlineStr">
+      <c r="M156" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N156" s="12" t="n"/>
       <c r="O156" s="12" t="n"/>
-      <c r="P156" s="12" t="n"/>
-      <c r="Q156" s="28" t="n"/>
-      <c r="R156" s="12" t="n"/>
+      <c r="P156" s="28" t="n"/>
+      <c r="Q156" s="12" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="12" t="inlineStr">
@@ -18162,16 +17593,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M157" s="12" t="inlineStr"/>
-      <c r="N157" s="27" t="inlineStr">
+      <c r="M157" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N157" s="12" t="n"/>
       <c r="O157" s="12" t="n"/>
-      <c r="P157" s="12" t="n"/>
-      <c r="Q157" s="28" t="n"/>
-      <c r="R157" s="12" t="n"/>
+      <c r="P157" s="28" t="n"/>
+      <c r="Q157" s="12" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="12" t="inlineStr">
@@ -18221,12 +17651,12 @@
       </c>
       <c r="J158" s="12" t="inlineStr">
         <is>
-          <t>1. As ins.a call the EB Home endpoint.</t>
+          <t>1. As ins.a send a direct EB Home request.</t>
         </is>
       </c>
       <c r="K158" s="12" t="inlineStr">
         <is>
-          <t>The call is refused.</t>
+          <t>The request is refused.</t>
         </is>
       </c>
       <c r="L158" s="12" t="inlineStr">
@@ -18234,23 +17664,22 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M158" s="12" t="inlineStr"/>
-      <c r="N158" s="27" t="inlineStr">
+      <c r="M158" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N158" s="12" t="n"/>
       <c r="O158" s="12" t="n"/>
-      <c r="P158" s="12" t="n"/>
-      <c r="Q158" s="28" t="n"/>
-      <c r="R158" s="12" t="n"/>
+      <c r="P158" s="28" t="n"/>
+      <c r="Q158" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R158"/>
+  <autoFilter ref="A4:Q158"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A2:Q2"/>
   </mergeCells>
-  <conditionalFormatting sqref="N5:N658">
+  <conditionalFormatting sqref="M5:M658">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -18264,19 +17693,19 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:R658">
+  <conditionalFormatting sqref="A5:Q658">
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="F5:F658" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Type" error="Choose a value from the list (Type)." type="list">
-      <formula1>'_lists'!$B$1:$B$7</formula1>
+      <formula1>'_lists'!$B$1:$B$9</formula1>
     </dataValidation>
     <dataValidation sqref="L5:L658" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'_lists'!$C$1:$C$3</formula1>
     </dataValidation>
-    <dataValidation sqref="N5:N658" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="M5:M658" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'_lists'!$D$1:$D$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -18300,7 +17729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18312,7 +17741,6 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -18339,7 +17767,6 @@
       <c r="G3" s="25" t="n"/>
       <c r="H3" s="25" t="n"/>
       <c r="I3" s="25" t="n"/>
-      <c r="J3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -18384,11 +17811,6 @@
       </c>
       <c r="I4" s="26" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="J4" s="26" t="inlineStr">
-        <is>
           <t>Coverage</t>
         </is>
       </c>
@@ -18426,10 +17848,7 @@
       <c r="H5" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="27" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -18468,10 +17887,7 @@
       <c r="H6" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="27" t="inlineStr">
+      <c r="I6" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -18510,10 +17926,7 @@
       <c r="H7" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="27" t="inlineStr">
+      <c r="I7" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -18552,10 +17965,7 @@
       <c r="H8" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="27" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -18594,10 +18004,7 @@
       <c r="H9" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="27" t="inlineStr">
+      <c r="I9" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -18636,10 +18043,7 @@
       <c r="H10" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="27" t="inlineStr">
+      <c r="I10" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -18678,10 +18082,7 @@
       <c r="H11" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="27" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -18720,10 +18121,7 @@
       <c r="H12" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="27" t="inlineStr">
+      <c r="I12" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -18762,10 +18160,7 @@
       <c r="H13" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="27" t="inlineStr">
+      <c r="I13" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -18804,10 +18199,7 @@
       <c r="H14" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="27" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -18846,10 +18238,7 @@
       <c r="H15" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="27" t="inlineStr">
+      <c r="I15" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -18888,10 +18277,7 @@
       <c r="H16" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="27" t="inlineStr">
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -18930,10 +18316,7 @@
       <c r="H17" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="27" t="inlineStr">
+      <c r="I17" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -18972,10 +18355,7 @@
       <c r="H18" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="27" t="inlineStr">
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19014,10 +18394,7 @@
       <c r="H19" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="27" t="inlineStr">
+      <c r="I19" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19056,10 +18433,7 @@
       <c r="H20" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="27" t="inlineStr">
+      <c r="I20" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19098,10 +18472,7 @@
       <c r="H21" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="27" t="inlineStr">
+      <c r="I21" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19140,10 +18511,7 @@
       <c r="H22" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="27" t="inlineStr">
+      <c r="I22" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19182,10 +18550,7 @@
       <c r="H23" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="27" t="inlineStr">
+      <c r="I23" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19224,10 +18589,7 @@
       <c r="H24" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="27" t="inlineStr">
+      <c r="I24" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19266,10 +18628,7 @@
       <c r="H25" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="27" t="inlineStr">
+      <c r="I25" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19308,10 +18667,7 @@
       <c r="H26" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="27" t="inlineStr">
+      <c r="I26" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19330,7 +18686,7 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Build and sign off the comparative analysis</t>
+          <t>Prepare and sign off the comparative analysis</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -19350,10 +18706,7 @@
       <c r="H27" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="27" t="inlineStr">
+      <c r="I27" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19392,10 +18745,7 @@
       <c r="H28" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="27" t="inlineStr">
+      <c r="I28" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19434,10 +18784,7 @@
       <c r="H29" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="27" t="inlineStr">
+      <c r="I29" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19476,10 +18823,7 @@
       <c r="H30" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="27" t="inlineStr">
+      <c r="I30" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19518,10 +18862,7 @@
       <c r="H31" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="27" t="inlineStr">
+      <c r="I31" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19560,10 +18901,7 @@
       <c r="H32" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="27" t="inlineStr">
+      <c r="I32" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19602,10 +18940,7 @@
       <c r="H33" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="27" t="inlineStr">
+      <c r="I33" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19644,10 +18979,7 @@
       <c r="H34" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="27" t="inlineStr">
+      <c r="I34" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19686,10 +19018,7 @@
       <c r="H35" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="27" t="inlineStr">
+      <c r="I35" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19728,10 +19057,7 @@
       <c r="H36" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="27" t="inlineStr">
+      <c r="I36" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19770,10 +19096,7 @@
       <c r="H37" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="27" t="inlineStr">
+      <c r="I37" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19812,10 +19135,7 @@
       <c r="H38" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="27" t="inlineStr">
+      <c r="I38" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19854,10 +19174,7 @@
       <c r="H39" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="27" t="inlineStr">
+      <c r="I39" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19896,10 +19213,7 @@
       <c r="H40" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="27" t="inlineStr">
+      <c r="I40" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19938,10 +19252,7 @@
       <c r="H41" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="27" t="inlineStr">
+      <c r="I41" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -19980,10 +19291,7 @@
       <c r="H42" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="27" t="inlineStr">
+      <c r="I42" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20022,10 +19330,7 @@
       <c r="H43" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="27" t="inlineStr">
+      <c r="I43" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20060,10 +19365,7 @@
       <c r="H44" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="27" t="inlineStr">
+      <c r="I44" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20098,10 +19400,7 @@
       <c r="H45" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="27" t="inlineStr">
+      <c r="I45" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20136,10 +19435,7 @@
       <c r="H46" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="27" t="inlineStr">
+      <c r="I46" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20174,10 +19470,7 @@
       <c r="H47" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="27" t="inlineStr">
+      <c r="I47" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20212,10 +19505,7 @@
       <c r="H48" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="27" t="inlineStr">
+      <c r="I48" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20250,10 +19540,7 @@
       <c r="H49" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="27" t="inlineStr">
+      <c r="I49" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20288,10 +19575,7 @@
       <c r="H50" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="27" t="inlineStr">
+      <c r="I50" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20326,10 +19610,7 @@
       <c r="H51" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="27" t="inlineStr">
+      <c r="I51" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20364,10 +19645,7 @@
       <c r="H52" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="27" t="inlineStr">
+      <c r="I52" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20402,10 +19680,7 @@
       <c r="H53" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="27" t="inlineStr">
+      <c r="I53" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20440,10 +19715,7 @@
       <c r="H54" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="27" t="inlineStr">
+      <c r="I54" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20478,10 +19750,7 @@
       <c r="H55" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="27" t="inlineStr">
+      <c r="I55" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20516,10 +19785,7 @@
       <c r="H56" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="27" t="inlineStr">
+      <c r="I56" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20554,10 +19820,7 @@
       <c r="H57" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="27" t="inlineStr">
+      <c r="I57" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20592,10 +19855,7 @@
       <c r="H58" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="27" t="inlineStr">
+      <c r="I58" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20630,10 +19890,7 @@
       <c r="H59" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="27" t="inlineStr">
+      <c r="I59" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20668,10 +19925,7 @@
       <c r="H60" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="27" t="inlineStr">
+      <c r="I60" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20706,10 +19960,7 @@
       <c r="H61" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="27" t="inlineStr">
+      <c r="I61" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20744,10 +19995,7 @@
       <c r="H62" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I62" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="27" t="inlineStr">
+      <c r="I62" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20782,10 +20030,7 @@
       <c r="H63" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I63" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="27" t="inlineStr">
+      <c r="I63" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20820,10 +20065,7 @@
       <c r="H64" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I64" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="27" t="inlineStr">
+      <c r="I64" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20858,10 +20100,7 @@
       <c r="H65" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="27" t="inlineStr">
+      <c r="I65" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20896,10 +20135,7 @@
       <c r="H66" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I66" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="27" t="inlineStr">
+      <c r="I66" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20934,10 +20170,7 @@
       <c r="H67" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="27" t="inlineStr">
+      <c r="I67" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -20972,10 +20205,7 @@
       <c r="H68" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I68" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="27" t="inlineStr">
+      <c r="I68" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21010,10 +20240,7 @@
       <c r="H69" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="27" t="inlineStr">
+      <c r="I69" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21048,10 +20275,7 @@
       <c r="H70" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I70" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="27" t="inlineStr">
+      <c r="I70" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21086,10 +20310,7 @@
       <c r="H71" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="27" t="inlineStr">
+      <c r="I71" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21124,10 +20345,7 @@
       <c r="H72" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="27" t="inlineStr">
+      <c r="I72" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21162,10 +20380,7 @@
       <c r="H73" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="27" t="inlineStr">
+      <c r="I73" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21200,10 +20415,7 @@
       <c r="H74" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I74" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="27" t="inlineStr">
+      <c r="I74" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21238,10 +20450,7 @@
       <c r="H75" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="27" t="inlineStr">
+      <c r="I75" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21276,10 +20485,7 @@
       <c r="H76" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I76" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="27" t="inlineStr">
+      <c r="I76" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -21314,32 +20520,29 @@
       <c r="H77" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="27" t="inlineStr">
+      <c r="I77" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J77"/>
+  <autoFilter ref="A4:I77"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J5:J577">
+  <conditionalFormatting sqref="I5:I577">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"GAP"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:J577">
+  <conditionalFormatting sqref="A5:I577">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J577" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coverage" error="Choose a value from the list (Coverage)." type="list">
+    <dataValidation sqref="I5:I577" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coverage" error="Choose a value from the list (Coverage)." type="list">
       <formula1>'_lists'!$E$1:$E$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -21651,7 +20854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -21661,12 +20864,11 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -21696,7 +20898,6 @@
       <c r="J3" s="25" t="n"/>
       <c r="K3" s="25" t="n"/>
       <c r="L3" s="25" t="n"/>
-      <c r="M3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -21736,32 +20937,27 @@
       </c>
       <c r="H4" s="26" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="I4" s="26" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="J4" s="26" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="K4" s="26" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="L4" s="26" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="M4" s="26" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
+          <t>Issue ID</t>
         </is>
       </c>
     </row>
@@ -21801,16 +20997,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr"/>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="28" t="n"/>
-      <c r="M5" s="12" t="n"/>
+      <c r="K5" s="28" t="n"/>
+      <c r="L5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -21845,19 +21040,18 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>The maker buttons are not shown; the calls return HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr"/>
-      <c r="I6" s="27" t="inlineStr">
+          <t>The maker buttons are not shown; direct requests are refused.</t>
+        </is>
+      </c>
+      <c r="H6" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I6" s="12" t="n"/>
       <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="28" t="n"/>
-      <c r="M6" s="12" t="n"/>
+      <c r="K6" s="28" t="n"/>
+      <c r="L6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -21892,19 +21086,18 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>The maker buttons are not shown; the calls return HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr"/>
-      <c r="I7" s="27" t="inlineStr">
+          <t>The maker buttons are not shown; direct requests are refused.</t>
+        </is>
+      </c>
+      <c r="H7" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I7" s="12" t="n"/>
       <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="28" t="n"/>
-      <c r="M7" s="12" t="n"/>
+      <c r="K7" s="28" t="n"/>
+      <c r="L7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -21939,19 +21132,18 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>The maker buttons are not shown; the calls return HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr"/>
-      <c r="I8" s="27" t="inlineStr">
+          <t>The maker buttons are not shown; direct requests are refused.</t>
+        </is>
+      </c>
+      <c r="H8" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I8" s="12" t="n"/>
       <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="28" t="n"/>
-      <c r="M8" s="12" t="n"/>
+      <c r="K8" s="28" t="n"/>
+      <c r="L8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -21986,19 +21178,18 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>The maker buttons are not shown; the calls return HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr"/>
-      <c r="I9" s="27" t="inlineStr">
+          <t>The maker buttons are not shown; direct requests are refused.</t>
+        </is>
+      </c>
+      <c r="H9" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I9" s="12" t="n"/>
       <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="28" t="n"/>
-      <c r="M9" s="12" t="n"/>
+      <c r="K9" s="28" t="n"/>
+      <c r="L9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -22036,16 +21227,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr"/>
-      <c r="I10" s="27" t="inlineStr">
+      <c r="H10" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="28" t="n"/>
-      <c r="M10" s="12" t="n"/>
+      <c r="K10" s="28" t="n"/>
+      <c r="L10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -22083,16 +21273,15 @@
           <t>Approve and Return are not shown.</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr"/>
-      <c r="I11" s="27" t="inlineStr">
+      <c r="H11" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="28" t="n"/>
-      <c r="M11" s="12" t="n"/>
+      <c r="K11" s="28" t="n"/>
+      <c r="L11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -22130,16 +21319,15 @@
           <t>Approve and Return are not shown.</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr"/>
-      <c r="I12" s="27" t="inlineStr">
+      <c r="H12" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I12" s="12" t="n"/>
       <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="28" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="K12" s="28" t="n"/>
+      <c r="L12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -22177,16 +21365,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr"/>
-      <c r="I13" s="27" t="inlineStr">
+      <c r="H13" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I13" s="12" t="n"/>
       <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="28" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="K13" s="28" t="n"/>
+      <c r="L13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -22224,16 +21411,15 @@
           <t>The item is not offered in My Approvals.</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr"/>
-      <c r="I14" s="27" t="inlineStr">
+      <c r="H14" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I14" s="12" t="n"/>
       <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="n"/>
-      <c r="L14" s="28" t="n"/>
-      <c r="M14" s="12" t="n"/>
+      <c r="K14" s="28" t="n"/>
+      <c r="L14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -22271,16 +21457,15 @@
           <t>The item is not offered in My Approvals.</t>
         </is>
       </c>
-      <c r="H15" s="12" t="inlineStr"/>
-      <c r="I15" s="27" t="inlineStr">
+      <c r="H15" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I15" s="12" t="n"/>
       <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="28" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="K15" s="28" t="n"/>
+      <c r="L15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -22318,16 +21503,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr"/>
-      <c r="I16" s="27" t="inlineStr">
+      <c r="H16" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I16" s="12" t="n"/>
       <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="28" t="n"/>
-      <c r="M16" s="12" t="n"/>
+      <c r="K16" s="28" t="n"/>
+      <c r="L16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -22365,16 +21549,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr"/>
-      <c r="I17" s="27" t="inlineStr">
+      <c r="H17" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I17" s="12" t="n"/>
       <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="28" t="n"/>
-      <c r="M17" s="12" t="n"/>
+      <c r="K17" s="28" t="n"/>
+      <c r="L17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -22412,16 +21595,15 @@
           <t>Validate and Release are not shown.</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr"/>
-      <c r="I18" s="27" t="inlineStr">
+      <c r="H18" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I18" s="12" t="n"/>
       <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="28" t="n"/>
-      <c r="M18" s="12" t="n"/>
+      <c r="K18" s="28" t="n"/>
+      <c r="L18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -22459,16 +21641,15 @@
           <t>Validate and Release are not shown.</t>
         </is>
       </c>
-      <c r="H19" s="12" t="inlineStr"/>
-      <c r="I19" s="27" t="inlineStr">
+      <c r="H19" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I19" s="12" t="n"/>
       <c r="J19" s="12" t="n"/>
-      <c r="K19" s="12" t="n"/>
-      <c r="L19" s="28" t="n"/>
-      <c r="M19" s="12" t="n"/>
+      <c r="K19" s="28" t="n"/>
+      <c r="L19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -22506,16 +21687,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr"/>
-      <c r="I20" s="27" t="inlineStr">
+      <c r="H20" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I20" s="12" t="n"/>
       <c r="J20" s="12" t="n"/>
-      <c r="K20" s="12" t="n"/>
-      <c r="L20" s="28" t="n"/>
-      <c r="M20" s="12" t="n"/>
+      <c r="K20" s="28" t="n"/>
+      <c r="L20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -22553,16 +21733,15 @@
           <t>The Collection acknowledgement is not shown.</t>
         </is>
       </c>
-      <c r="H21" s="12" t="inlineStr"/>
-      <c r="I21" s="27" t="inlineStr">
+      <c r="H21" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I21" s="12" t="n"/>
       <c r="J21" s="12" t="n"/>
-      <c r="K21" s="12" t="n"/>
-      <c r="L21" s="28" t="n"/>
-      <c r="M21" s="12" t="n"/>
+      <c r="K21" s="28" t="n"/>
+      <c r="L21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -22600,16 +21779,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H22" s="12" t="inlineStr"/>
-      <c r="I22" s="27" t="inlineStr">
+      <c r="H22" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I22" s="12" t="n"/>
       <c r="J22" s="12" t="n"/>
-      <c r="K22" s="12" t="n"/>
-      <c r="L22" s="28" t="n"/>
-      <c r="M22" s="12" t="n"/>
+      <c r="K22" s="28" t="n"/>
+      <c r="L22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -22647,16 +21825,15 @@
           <t>EB Setup is not in the menu.</t>
         </is>
       </c>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="27" t="inlineStr">
+      <c r="H23" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I23" s="12" t="n"/>
       <c r="J23" s="12" t="n"/>
-      <c r="K23" s="12" t="n"/>
-      <c r="L23" s="28" t="n"/>
-      <c r="M23" s="12" t="n"/>
+      <c r="K23" s="28" t="n"/>
+      <c r="L23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -22694,16 +21871,15 @@
           <t>EB Setup is not in the menu.</t>
         </is>
       </c>
-      <c r="H24" s="12" t="inlineStr"/>
-      <c r="I24" s="27" t="inlineStr">
+      <c r="H24" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I24" s="12" t="n"/>
       <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
-      <c r="L24" s="28" t="n"/>
-      <c r="M24" s="12" t="n"/>
+      <c r="K24" s="28" t="n"/>
+      <c r="L24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -22741,16 +21917,15 @@
           <t>EB Setup is not in the menu.</t>
         </is>
       </c>
-      <c r="H25" s="12" t="inlineStr"/>
-      <c r="I25" s="27" t="inlineStr">
+      <c r="H25" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I25" s="12" t="n"/>
       <c r="J25" s="12" t="n"/>
-      <c r="K25" s="12" t="n"/>
-      <c r="L25" s="28" t="n"/>
-      <c r="M25" s="12" t="n"/>
+      <c r="K25" s="28" t="n"/>
+      <c r="L25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -22788,16 +21963,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr"/>
-      <c r="I26" s="27" t="inlineStr">
+      <c r="H26" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I26" s="12" t="n"/>
       <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="28" t="n"/>
-      <c r="M26" s="12" t="n"/>
+      <c r="K26" s="28" t="n"/>
+      <c r="L26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -22835,16 +22009,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H27" s="12" t="inlineStr"/>
-      <c r="I27" s="27" t="inlineStr">
+      <c r="H27" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I27" s="12" t="n"/>
       <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
-      <c r="L27" s="28" t="n"/>
-      <c r="M27" s="12" t="n"/>
+      <c r="K27" s="28" t="n"/>
+      <c r="L27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -22882,16 +22055,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H28" s="12" t="inlineStr"/>
-      <c r="I28" s="27" t="inlineStr">
+      <c r="H28" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I28" s="12" t="n"/>
       <c r="J28" s="12" t="n"/>
-      <c r="K28" s="12" t="n"/>
-      <c r="L28" s="28" t="n"/>
-      <c r="M28" s="12" t="n"/>
+      <c r="K28" s="28" t="n"/>
+      <c r="L28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -22929,16 +22101,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H29" s="12" t="inlineStr"/>
-      <c r="I29" s="27" t="inlineStr">
+      <c r="H29" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I29" s="12" t="n"/>
       <c r="J29" s="12" t="n"/>
-      <c r="K29" s="12" t="n"/>
-      <c r="L29" s="28" t="n"/>
-      <c r="M29" s="12" t="n"/>
+      <c r="K29" s="28" t="n"/>
+      <c r="L29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -22973,19 +22144,18 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>The Employee Benefits category is not listed; the run call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr"/>
-      <c r="I30" s="27" t="inlineStr">
+          <t>The Employee Benefits category is not listed; a direct run request is refused.</t>
+        </is>
+      </c>
+      <c r="H30" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I30" s="12" t="n"/>
       <c r="J30" s="12" t="n"/>
-      <c r="K30" s="12" t="n"/>
-      <c r="L30" s="28" t="n"/>
-      <c r="M30" s="12" t="n"/>
+      <c r="K30" s="28" t="n"/>
+      <c r="L30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -23020,19 +22190,18 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>The Employee Benefits category is not listed; the run call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H31" s="12" t="inlineStr"/>
-      <c r="I31" s="27" t="inlineStr">
+          <t>The Employee Benefits category is not listed; a direct run request is refused.</t>
+        </is>
+      </c>
+      <c r="H31" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I31" s="12" t="n"/>
       <c r="J31" s="12" t="n"/>
-      <c r="K31" s="12" t="n"/>
-      <c r="L31" s="28" t="n"/>
-      <c r="M31" s="12" t="n"/>
+      <c r="K31" s="28" t="n"/>
+      <c r="L31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -23070,16 +22239,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H32" s="12" t="inlineStr"/>
-      <c r="I32" s="27" t="inlineStr">
+      <c r="H32" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I32" s="12" t="n"/>
       <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12" t="n"/>
-      <c r="L32" s="28" t="n"/>
-      <c r="M32" s="12" t="n"/>
+      <c r="K32" s="28" t="n"/>
+      <c r="L32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -23117,16 +22285,15 @@
           <t>User type External is not offered.</t>
         </is>
       </c>
-      <c r="H33" s="12" t="inlineStr"/>
-      <c r="I33" s="27" t="inlineStr">
+      <c r="H33" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I33" s="12" t="n"/>
       <c r="J33" s="12" t="n"/>
-      <c r="K33" s="12" t="n"/>
-      <c r="L33" s="28" t="n"/>
-      <c r="M33" s="12" t="n"/>
+      <c r="K33" s="28" t="n"/>
+      <c r="L33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -23164,16 +22331,15 @@
           <t>User type External is not offered.</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr"/>
-      <c r="I34" s="27" t="inlineStr">
+      <c r="H34" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I34" s="12" t="n"/>
       <c r="J34" s="12" t="n"/>
-      <c r="K34" s="12" t="n"/>
-      <c r="L34" s="28" t="n"/>
-      <c r="M34" s="12" t="n"/>
+      <c r="K34" s="28" t="n"/>
+      <c r="L34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -23211,16 +22377,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H35" s="12" t="inlineStr"/>
-      <c r="I35" s="27" t="inlineStr">
+      <c r="H35" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I35" s="12" t="n"/>
       <c r="J35" s="12" t="n"/>
-      <c r="K35" s="12" t="n"/>
-      <c r="L35" s="28" t="n"/>
-      <c r="M35" s="12" t="n"/>
+      <c r="K35" s="28" t="n"/>
+      <c r="L35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -23258,16 +22423,15 @@
           <t>The request is not offered for decision.</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr"/>
-      <c r="I36" s="27" t="inlineStr">
+      <c r="H36" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I36" s="12" t="n"/>
       <c r="J36" s="12" t="n"/>
-      <c r="K36" s="12" t="n"/>
-      <c r="L36" s="28" t="n"/>
-      <c r="M36" s="12" t="n"/>
+      <c r="K36" s="28" t="n"/>
+      <c r="L36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -23305,16 +22469,15 @@
           <t>The request is not offered for decision.</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr"/>
-      <c r="I37" s="27" t="inlineStr">
+      <c r="H37" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I37" s="12" t="n"/>
       <c r="J37" s="12" t="n"/>
-      <c r="K37" s="12" t="n"/>
-      <c r="L37" s="28" t="n"/>
-      <c r="M37" s="12" t="n"/>
+      <c r="K37" s="28" t="n"/>
+      <c r="L37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -23352,16 +22515,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr"/>
-      <c r="I38" s="27" t="inlineStr">
+      <c r="H38" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I38" s="12" t="n"/>
       <c r="J38" s="12" t="n"/>
-      <c r="K38" s="12" t="n"/>
-      <c r="L38" s="28" t="n"/>
-      <c r="M38" s="12" t="n"/>
+      <c r="K38" s="28" t="n"/>
+      <c r="L38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -23399,16 +22561,15 @@
           <t>Portal Users is not in the menu.</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr"/>
-      <c r="I39" s="27" t="inlineStr">
+      <c r="H39" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I39" s="12" t="n"/>
       <c r="J39" s="12" t="n"/>
-      <c r="K39" s="12" t="n"/>
-      <c r="L39" s="28" t="n"/>
-      <c r="M39" s="12" t="n"/>
+      <c r="K39" s="28" t="n"/>
+      <c r="L39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -23446,16 +22607,15 @@
           <t>Portal Users is not in the menu.</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr"/>
-      <c r="I40" s="27" t="inlineStr">
+      <c r="H40" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I40" s="12" t="n"/>
       <c r="J40" s="12" t="n"/>
-      <c r="K40" s="12" t="n"/>
-      <c r="L40" s="28" t="n"/>
-      <c r="M40" s="12" t="n"/>
+      <c r="K40" s="28" t="n"/>
+      <c r="L40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -23493,16 +22653,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H41" s="12" t="inlineStr"/>
-      <c r="I41" s="27" t="inlineStr">
+      <c r="H41" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I41" s="12" t="n"/>
       <c r="J41" s="12" t="n"/>
-      <c r="K41" s="12" t="n"/>
-      <c r="L41" s="28" t="n"/>
-      <c r="M41" s="12" t="n"/>
+      <c r="K41" s="28" t="n"/>
+      <c r="L41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -23540,16 +22699,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H42" s="12" t="inlineStr"/>
-      <c r="I42" s="27" t="inlineStr">
+      <c r="H42" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I42" s="12" t="n"/>
       <c r="J42" s="12" t="n"/>
-      <c r="K42" s="12" t="n"/>
-      <c r="L42" s="28" t="n"/>
-      <c r="M42" s="12" t="n"/>
+      <c r="K42" s="28" t="n"/>
+      <c r="L42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -23587,16 +22745,15 @@
           <t>Assign and Reassign are not shown.</t>
         </is>
       </c>
-      <c r="H43" s="12" t="inlineStr"/>
-      <c r="I43" s="27" t="inlineStr">
+      <c r="H43" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I43" s="12" t="n"/>
       <c r="J43" s="12" t="n"/>
-      <c r="K43" s="12" t="n"/>
-      <c r="L43" s="28" t="n"/>
-      <c r="M43" s="12" t="n"/>
+      <c r="K43" s="28" t="n"/>
+      <c r="L43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -23634,16 +22791,15 @@
           <t>Assign and Reassign are not shown.</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr"/>
-      <c r="I44" s="27" t="inlineStr">
+      <c r="H44" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I44" s="12" t="n"/>
       <c r="J44" s="12" t="n"/>
-      <c r="K44" s="12" t="n"/>
-      <c r="L44" s="28" t="n"/>
-      <c r="M44" s="12" t="n"/>
+      <c r="K44" s="28" t="n"/>
+      <c r="L44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -23681,16 +22837,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H45" s="12" t="inlineStr"/>
-      <c r="I45" s="27" t="inlineStr">
+      <c r="H45" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I45" s="12" t="n"/>
       <c r="J45" s="12" t="n"/>
-      <c r="K45" s="12" t="n"/>
-      <c r="L45" s="28" t="n"/>
-      <c r="M45" s="12" t="n"/>
+      <c r="K45" s="28" t="n"/>
+      <c r="L45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -23728,16 +22883,15 @@
           <t>The insurer pages are not offered to a client HR user.</t>
         </is>
       </c>
-      <c r="H46" s="12" t="inlineStr"/>
-      <c r="I46" s="27" t="inlineStr">
+      <c r="H46" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I46" s="12" t="n"/>
       <c r="J46" s="12" t="n"/>
-      <c r="K46" s="12" t="n"/>
-      <c r="L46" s="28" t="n"/>
-      <c r="M46" s="12" t="n"/>
+      <c r="K46" s="28" t="n"/>
+      <c r="L46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -23775,16 +22929,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H47" s="12" t="inlineStr"/>
-      <c r="I47" s="27" t="inlineStr">
+      <c r="H47" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I47" s="12" t="n"/>
       <c r="J47" s="12" t="n"/>
-      <c r="K47" s="12" t="n"/>
-      <c r="L47" s="28" t="n"/>
-      <c r="M47" s="12" t="n"/>
+      <c r="K47" s="28" t="n"/>
+      <c r="L47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -23822,23 +22975,22 @@
           <t>The client pages are not offered to an insurer user.</t>
         </is>
       </c>
-      <c r="H48" s="12" t="inlineStr"/>
-      <c r="I48" s="27" t="inlineStr">
+      <c r="H48" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I48" s="12" t="n"/>
       <c r="J48" s="12" t="n"/>
-      <c r="K48" s="12" t="n"/>
-      <c r="L48" s="28" t="n"/>
-      <c r="M48" s="12" t="n"/>
+      <c r="K48" s="28" t="n"/>
+      <c r="L48" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M48"/>
+  <autoFilter ref="A4:L48"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I548">
+  <conditionalFormatting sqref="H5:H548">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -23852,7 +23004,7 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:M548">
+  <conditionalFormatting sqref="A5:L548">
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -23861,7 +23013,7 @@
     <dataValidation sqref="F5:F548" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Access" error="Choose a value from the list (Access)." type="list">
       <formula1>'_lists'!$F$1:$F$2</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I548" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="H5:H548" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'_lists'!$G$1:$G$5</formula1>
     </dataValidation>
   </dataValidations>
